--- a/resource/Script/script_InertiaLucis.xlsx
+++ b/resource/Script/script_InertiaLucis.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\usosctheater\resource\Script\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D20588AC-74BA-4B45-BCA8-3496404040D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{359DB2D5-75D5-48BC-ACB7-64F0B6F9E26F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11340" yWindow="1050" windowWidth="30375" windowHeight="15345" xr2:uid="{12160F34-6A21-4287-85A5-86880D8D3A1A}"/>
+    <workbookView xWindow="2160" yWindow="1545" windowWidth="30375" windowHeight="15345" xr2:uid="{12160F34-6A21-4287-85A5-86880D8D3A1A}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Script_Demo" sheetId="2" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,16 +28,887 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="264">
+  <si>
+    <t>se_trans_out|se_trans_in</t>
+  </si>
+  <si>
+    <t>wipe_left</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>TRANSITION</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>anger1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>right</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>asahi_idol_3</t>
+  </si>
+  <si>
+    <t>s001085</t>
+  </si>
+  <si>
+    <t>무리임다, 그런 거~</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>아사히</t>
+  </si>
+  <si>
+    <t>TEXT</t>
+  </si>
+  <si>
+    <t>anger3</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>left</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>fuyuko_idol_3</t>
+  </si>
+  <si>
+    <t>s001084</t>
+  </si>
+  <si>
+    <t>너가 그만큼 열심히 달리면 되잖아!</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>후유코</t>
+  </si>
+  <si>
+    <t>s001083</t>
+  </si>
+  <si>
+    <t>에~ 1등 아니면 재미 없슴다~</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>smile2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>center</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mei_idol_3</t>
+  </si>
+  <si>
+    <t>s001082</t>
+  </si>
+  <si>
+    <t>아하하, 후유코쨩… 진정 진정~</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>메이</t>
+  </si>
+  <si>
+    <t>s001081</t>
+  </si>
+  <si>
+    <t>시끄러! 알고 있거든!</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>s001080</t>
+  </si>
+  <si>
+    <t>그치만, 후유코쨩 느리니까 1등은 못할 것 같슴다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>wait1 face_serious lip_surp</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>s001079</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>감사함다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.3</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>se_tansan</t>
+  </si>
+  <si>
+    <t>SE</t>
+  </si>
+  <si>
+    <t>s001078</t>
+  </si>
+  <si>
+    <t>자, 이거.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>s001077</t>
+  </si>
+  <si>
+    <t>재밌게 달리기만 하면 되니까.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>shrug</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>s001076</t>
+  </si>
+  <si>
+    <t>몰라도 돼, 너는.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>think1 lip_surp</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>s001075</t>
+  </si>
+  <si>
+    <t>… 잘 모르겠슴다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>s001074</t>
+  </si>
+  <si>
+    <t>죽을만큼 하기 싫어도, 해야 하는 일이라면 후유는 할 거야.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>s001073</t>
+  </si>
+  <si>
+    <t>어른에게는 하기 싫어도 해야 하는 일이라는 게 있거든.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>wait4</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>s001072</t>
+  </si>
+  <si>
+    <t>바보네.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>none</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>s001071</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>후유코쨩이 하기 싫은 거라면…</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>bg_hikaesitu</t>
+  </si>
+  <si>
+    <t>1.5</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>zoom</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>BG</t>
+  </si>
+  <si>
+    <t>s001070</t>
+  </si>
+  <si>
+    <t>그런 거, 전혀 재미있지 않슴다…</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>s001069</t>
+  </si>
+  <si>
+    <t>하기 싫은데 억지로 나가는 건, 이상함다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>s001068</t>
+  </si>
+  <si>
+    <t>후유코쨩.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>wait3 face_sad lip_anger2</t>
+  </si>
+  <si>
+    <t>s001067</t>
+  </si>
+  <si>
+    <t>그치만 후유코쨩이…</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>TEXT</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>anger2 face_cry lip_sad</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>s001066</t>
+  </si>
+  <si>
+    <t>괜히 나중에 말을 바꿔서 나쁜 인상을 주고 싶지도 않고.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>s001065</t>
+  </si>
+  <si>
+    <t>스트레이라이트의 인지도를 올릴 좋은 기회야.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>wait2 face_serious lip_sad</t>
+  </si>
+  <si>
+    <t>s001064</t>
+  </si>
+  <si>
+    <t>PD님이 이야기한 것처럼, 이 녀석이 주목 받을 건 거의 확실하니까.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>s001063</t>
+  </si>
+  <si>
+    <t>거기에 이번에는 원샷 카메라까지 받을 수 있다며?</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>s001062</t>
+  </si>
+  <si>
+    <t>메이가 이야기했듯이, 이어달리기는 운동회의 꽃이니까.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>wait4 lip_anger</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>s001061</t>
+  </si>
+  <si>
+    <t>후유가 좋고 싫고 이전에, 이건 확실히 좋은 기회야.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>s001060</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>아니.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>BREAK</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>s001059</t>
+  </si>
+  <si>
+    <t>나가는 종목에 대해서는 조금 더 생각해보겠다고 지금이라도 이야기하면…</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>프로듀서</t>
+  </si>
+  <si>
+    <t>s001058</t>
+  </si>
+  <si>
+    <t>그 분위기에서 나가기 싫다고 할 수 있겠냐고!</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>wait lip_surp</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>center</t>
+  </si>
+  <si>
+    <t>s001057</t>
+  </si>
+  <si>
+    <t>그치만 나가겠다고 한 건 후유코쨩임다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>s001056</t>
+  </si>
+  <si>
+    <t>왜 후유가 이 녀석 때문에 이어달리기에 나가야 되는 건데</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>shrug2 lip_anger</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>s001055</t>
+  </si>
+  <si>
+    <t>괜찮을 리가 없잖아.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>wait1 face_serious lip_anger2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>s001054</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>후유코쨩, 정말 괜찮아?</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>BGM_100</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>BGM</t>
+  </si>
+  <si>
+    <t>iris</t>
+  </si>
+  <si>
+    <t>door_sime</t>
+  </si>
+  <si>
+    <t>smile1</t>
+  </si>
+  <si>
+    <t>left</t>
+  </si>
+  <si>
+    <t>s001053</t>
+  </si>
+  <si>
+    <t>네, 잘 부탁드립니다~</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>s001052</t>
+  </si>
+  <si>
+    <t>아하하, 좋네! 그럼 다음 달에 잘 부탁해!</t>
+  </si>
+  <si>
+    <t>방송 PD</t>
+  </si>
+  <si>
+    <t>s001051</t>
+  </si>
+  <si>
+    <t>후유코…?</t>
+  </si>
+  <si>
+    <t>surp1</t>
+  </si>
+  <si>
+    <t>right</t>
+  </si>
+  <si>
+    <t>s001050</t>
+  </si>
+  <si>
+    <t>후, 후유코쨩…?</t>
+  </si>
+  <si>
+    <t>s001049</t>
+  </si>
+  <si>
+    <t>네. 저희한테 맡겨주세요.</t>
+  </si>
+  <si>
+    <t>wait1 face_surp lip_surp</t>
+  </si>
+  <si>
+    <t>s001048</t>
+  </si>
+  <si>
+    <t>아, 그건…</t>
+  </si>
+  <si>
+    <t>s001047</t>
+  </si>
+  <si>
+    <t>P, PD님, 잠시…</t>
+  </si>
+  <si>
+    <t>s001046</t>
+  </si>
+  <si>
+    <t>두 사람도 괜찮지? 운동 잘 하잖아?</t>
+  </si>
+  <si>
+    <t>s001045</t>
+  </si>
+  <si>
+    <t>스트레이라이트한테는 꼭 이어달리기에 나가줬으면 해서!</t>
+  </si>
+  <si>
+    <t>s001044</t>
+  </si>
+  <si>
+    <t>어, 마침 잘 왔네!</t>
+  </si>
+  <si>
+    <t>s001043</t>
+  </si>
+  <si>
+    <t>PD님이랑 아사히가 다음 달에 나갈 운동회 이야기를 하고 있던 중이었는데…</t>
+  </si>
+  <si>
+    <t>s001042</t>
+  </si>
+  <si>
+    <t>아 후유코, 메이. 어서 와.</t>
+  </si>
+  <si>
+    <t>wait1 face_smile lip_bitter_smile</t>
+  </si>
+  <si>
+    <t>s001041</t>
+  </si>
+  <si>
+    <t>저기, 프로듀서 님… 이건…?</t>
+  </si>
+  <si>
+    <t>anger1</t>
+  </si>
+  <si>
+    <t>s001040</t>
+  </si>
+  <si>
+    <t>다음 달까지는 못 기다림다~</t>
+  </si>
+  <si>
+    <t>wait2</t>
+  </si>
+  <si>
+    <t>s001039</t>
+  </si>
+  <si>
+    <t>수고하십니다.</t>
+  </si>
+  <si>
+    <t>s001038</t>
+  </si>
+  <si>
+    <t>수고하십니다~</t>
+  </si>
+  <si>
+    <t>door_knock</t>
+  </si>
+  <si>
+    <t>normal</t>
+  </si>
+  <si>
+    <t>s001037</t>
+  </si>
+  <si>
+    <t>아쉽게도 다음 달 대여 예정이라서</t>
+  </si>
+  <si>
+    <t>s001036</t>
+  </si>
+  <si>
+    <t>빨리 승부하고 싶슴다!</t>
+  </si>
+  <si>
+    <t>smile3 lip_wait</t>
+  </si>
+  <si>
+    <t>s001035</t>
+  </si>
+  <si>
+    <t>그 트랙… 무슨 카메라는 지금 어디있슴까?</t>
+  </si>
+  <si>
+    <t>s001034</t>
+  </si>
+  <si>
+    <t>아하하! 그렇네, 아사히쨩이 이길 수 있다면 말이지!</t>
+  </si>
+  <si>
+    <t>skill1</t>
+  </si>
+  <si>
+    <t>s001033</t>
+  </si>
+  <si>
+    <t>그럼, 그 녀석을 이기면 제가 1등인 거네요?</t>
+  </si>
+  <si>
+    <t>s001032</t>
+  </si>
+  <si>
+    <t>그야 달리는 선수들을 찍어야 하니까 당연히…</t>
+  </si>
+  <si>
+    <t>think1</t>
+  </si>
+  <si>
+    <t>s001031</t>
+  </si>
+  <si>
+    <t>그 트랙 러너 카메라라는 거, 빠른 검까?</t>
+  </si>
+  <si>
+    <t>s001030</t>
+  </si>
+  <si>
+    <t>지금은 보통 트랙 러너 카메라라는 녀석으로 찍거든</t>
+  </si>
+  <si>
+    <t>s001029</t>
+  </si>
+  <si>
+    <t>뭐, 옛날에는 직접 들고 뛰었을지도 모르겠지만</t>
+  </si>
+  <si>
+    <t>sad2 lip_anger</t>
+  </si>
+  <si>
+    <t>s001028</t>
+  </si>
+  <si>
+    <t>뭐야, 직접 뛰는 건 줄 알았슴다…</t>
+  </si>
+  <si>
+    <t>s001027</t>
+  </si>
+  <si>
+    <t>아니, 아무리 그래도 직접 들고 뛰진 않지~</t>
+  </si>
+  <si>
+    <t>s001026</t>
+  </si>
+  <si>
+    <t>카메라 감독님이 카메라를 들고 선수보다 빨리 뛰는 거!</t>
+  </si>
+  <si>
+    <t>s001025</t>
+  </si>
+  <si>
+    <t>그거, 본 적 있슴다!</t>
+  </si>
+  <si>
+    <t>s001024</t>
+  </si>
+  <si>
+    <t>이번에는 이어달리기용 원샷 카메라도 준비해뒀다고!</t>
+  </si>
+  <si>
+    <t>s001023</t>
+  </si>
+  <si>
+    <t>작년 방송이 꽤 화제가 돼서 말이야.</t>
+  </si>
+  <si>
+    <t>s001022</t>
+  </si>
+  <si>
+    <t>아사히쨩이 달리는 거, 분명 그림이 될 테니까!</t>
+  </si>
+  <si>
+    <t>s001021</t>
+  </si>
+  <si>
+    <t>와하하! 좋네, 그거!</t>
+  </si>
+  <si>
+    <t>wait1 face_smile</t>
+  </si>
+  <si>
+    <t>BGM_nanndesyou</t>
+  </si>
+  <si>
+    <t>s001020</t>
+  </si>
+  <si>
+    <t>자, 잠깐만 후유코쨩!</t>
+  </si>
+  <si>
+    <t>se_rouka_run</t>
+  </si>
+  <si>
+    <t>bg_rouka</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>wait4 face_jito lip_anger</t>
+  </si>
+  <si>
+    <t>s001019</t>
+  </si>
+  <si>
+    <t>왠지 불길한 기분이 들어… 빨리 돌아가자.</t>
+  </si>
+  <si>
+    <t>wait1 face_surp</t>
+  </si>
+  <si>
+    <t>s001018</t>
+  </si>
+  <si>
+    <t>후유코쨩?</t>
+  </si>
+  <si>
+    <t>shrug face_serious lip_sad</t>
+  </si>
+  <si>
+    <t>s001017</t>
+  </si>
+  <si>
+    <t>잠깐만, 메이.</t>
+  </si>
+  <si>
+    <t>s001016</t>
+  </si>
+  <si>
+    <t>그 녀석 성격 상, 무조건 그렇겠지…</t>
+  </si>
+  <si>
+    <t>skill2 face_sad</t>
+  </si>
+  <si>
+    <t>s001015</t>
+  </si>
+  <si>
+    <t>아, 근데 아사히쨩은 분명 이어달리기 나가고 싶어할 텐데…</t>
+  </si>
+  <si>
+    <t>smile2</t>
+  </si>
+  <si>
+    <t>s001014</t>
+  </si>
+  <si>
+    <t>그렇구나… 후유코쨩이 그렇다면 이어달리기는 안 나가는 걸로!</t>
+  </si>
+  <si>
+    <t>s001013</t>
+  </si>
+  <si>
+    <t>팬들에게 완벽하지 않은 모습은 보여주고 싶지 않아.</t>
+  </si>
+  <si>
+    <t>s001012</t>
+  </si>
+  <si>
+    <t>애초에 후유, 달리기 그렇게 잘 하는 편이 아니니까…</t>
+  </si>
+  <si>
+    <t>wait1 face_jito lip_cry</t>
+  </si>
+  <si>
+    <t>s001011</t>
+  </si>
+  <si>
+    <t>그러니까 싫은 거야. 그렇게 보는 눈이 많은 곳에서 넘어지기라도 해 봐.</t>
+  </si>
+  <si>
+    <t>s001010</t>
+  </si>
+  <si>
+    <t>에, 정말? 계주는 운동회의 꽃이잖아?</t>
+  </si>
+  <si>
+    <t>s001009</t>
+  </si>
+  <si>
+    <t>아… 최악이야. 계주같은 건, 죽어도 사양이야</t>
+  </si>
+  <si>
+    <t>wait1</t>
+  </si>
+  <si>
+    <t>s001008</t>
+  </si>
+  <si>
+    <t>계주라던가, 어때?</t>
+  </si>
+  <si>
+    <t>think</t>
+  </si>
+  <si>
+    <t>s001007</t>
+  </si>
+  <si>
+    <t>음… 그러네…</t>
+  </si>
+  <si>
+    <t>1.5</t>
+  </si>
+  <si>
+    <t>zoom</t>
+  </si>
+  <si>
+    <t>s001006</t>
+  </si>
+  <si>
+    <t>후유코쨩은 뭐 나가고 싶어?</t>
+  </si>
+  <si>
+    <t>s001005</t>
+  </si>
+  <si>
+    <t>이번에는 유닛 별로 종목을 고를 수 있대~</t>
+  </si>
+  <si>
+    <t>s001004</t>
+  </si>
+  <si>
+    <t>아 그러고보니…</t>
+  </si>
+  <si>
+    <t>s001003</t>
+  </si>
+  <si>
+    <t>다음 달에 있는 운동회 이야기!</t>
+  </si>
+  <si>
+    <t>s001002</t>
+  </si>
+  <si>
+    <t>그거?</t>
+  </si>
+  <si>
+    <t>s001001</t>
+  </si>
+  <si>
+    <t>아 후유코쨩, 그거 들었어?</t>
+  </si>
+  <si>
+    <t>se_jihannki</t>
+  </si>
+  <si>
+    <t>Key</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Volume</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Track</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpeakerType</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Duration</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Value</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effect</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Animation</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Position</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>CG</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Voice</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Text</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Name</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Type</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="14"/>
       <color theme="1"/>
@@ -65,6 +937,19 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="넥슨Lv2고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="넥슨Lv2고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -86,12 +971,32 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -106,9 +1011,30 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -116,7 +1042,11 @@
     <cellStyle name="Title" xfId="2" xr:uid="{1A64B405-E2AD-4572-9CF8-360F00D5A551}"/>
     <cellStyle name="표준" xfId="0" builtinId="0" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -127,6 +1057,30 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{667B60E9-BAF9-45E8-BAE4-6BF792A4260E}" name="표1" displayName="표1" ref="B2:P113" totalsRowShown="0" headerRowDxfId="0" headerRowCellStyle="HeadLine">
+  <autoFilter ref="B2:P113" xr:uid="{160FF696-8FC2-44DF-96A2-501D4731471F}"/>
+  <tableColumns count="15">
+    <tableColumn id="1" xr3:uid="{F024CDFB-5FBA-43BE-BDFD-3D0EC697E324}" name="Type"/>
+    <tableColumn id="2" xr3:uid="{73C7A17F-D221-4CF8-B42F-2876AEAC322B}" name="Name"/>
+    <tableColumn id="3" xr3:uid="{DD550F31-322F-4817-807E-AAF3E6CF0FFF}" name="Text"/>
+    <tableColumn id="4" xr3:uid="{CDF95646-B83D-495D-BD41-06D7D3A95C54}" name="Voice"/>
+    <tableColumn id="5" xr3:uid="{A1147BB2-0A7B-4622-BBAA-91570393BF78}" name="CG"/>
+    <tableColumn id="6" xr3:uid="{4155DD9B-C05C-434F-A609-1CEAC810DDB9}" name="Position"/>
+    <tableColumn id="7" xr3:uid="{8BA44913-D749-4A3E-80D0-3168A1F34D0C}" name="Animation"/>
+    <tableColumn id="8" xr3:uid="{11225872-C73D-45E3-8E99-BB2E74DB7DC5}" name="Effect"/>
+    <tableColumn id="9" xr3:uid="{E39B4478-B8F4-473F-AC5F-B034D6CA7849}" name="Value"/>
+    <tableColumn id="10" xr3:uid="{2F734473-8501-4E3D-841A-731E04785078}" name="Duration"/>
+    <tableColumn id="11" xr3:uid="{0FE56BB9-365C-4107-9D7D-F50088A6DF87}" name="SpeakerType"/>
+    <tableColumn id="12" xr3:uid="{179D82E1-B734-4421-85E0-55BA17590B22}" name="Track"/>
+    <tableColumn id="13" xr3:uid="{44E25104-104B-4E0B-B46E-D8BC95108BFE}" name="Volume"/>
+    <tableColumn id="14" xr3:uid="{905C58BC-925F-41E8-8E03-FF9DF0EC66AE}" name="SE"/>
+    <tableColumn id="15" xr3:uid="{A7F805DD-14D9-478F-8616-C2F64F1371E4}" name="Key"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -425,6 +1379,3191 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C94EB75-B998-41E8-BC4A-4E72E7F17445}">
+  <dimension ref="B2:P113"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="51.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.4140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="26.58203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.4140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.08203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.75" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="20.58203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B2" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="J2" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="K2" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="L2" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="M2" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="N2" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="O2" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="P2" s="7" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="3" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B3" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="O3" s="1"/>
+      <c r="P3" s="1"/>
+    </row>
+    <row r="4" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B4" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
+      <c r="O4" s="1"/>
+      <c r="P4" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="5" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="N5" s="1"/>
+      <c r="O5" s="1"/>
+      <c r="P5" s="1"/>
+    </row>
+    <row r="6" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1"/>
+    </row>
+    <row r="7" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1"/>
+      <c r="O7" s="1"/>
+      <c r="P7" s="1"/>
+    </row>
+    <row r="8" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
+      <c r="O8" s="1"/>
+      <c r="P8" s="1"/>
+    </row>
+    <row r="9" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1"/>
+    </row>
+    <row r="10" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1"/>
+      <c r="O10" s="1"/>
+      <c r="P10" s="1"/>
+    </row>
+    <row r="11" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
+      <c r="P11" s="1"/>
+    </row>
+    <row r="12" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B12" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="1"/>
+      <c r="O12" s="1"/>
+      <c r="P12" s="1"/>
+    </row>
+    <row r="13" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B13" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
+      <c r="O13" s="1"/>
+      <c r="P13" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="14" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B14" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="O14" s="1"/>
+      <c r="P14" s="1"/>
+    </row>
+    <row r="15" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M15" s="1"/>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1"/>
+    </row>
+    <row r="16" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B16" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M16" s="1"/>
+      <c r="N16" s="1"/>
+      <c r="O16" s="1"/>
+      <c r="P16" s="1"/>
+    </row>
+    <row r="17" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B17" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1"/>
+      <c r="L17" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M17" s="1"/>
+      <c r="N17" s="1"/>
+      <c r="O17" s="1"/>
+      <c r="P17" s="1"/>
+    </row>
+    <row r="18" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B18" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M18" s="1"/>
+      <c r="N18" s="1"/>
+      <c r="O18" s="1"/>
+      <c r="P18" s="1"/>
+    </row>
+    <row r="19" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B19" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
+      <c r="O19" s="1"/>
+      <c r="P19" s="1"/>
+    </row>
+    <row r="20" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B20" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1"/>
+      <c r="O20" s="1"/>
+      <c r="P20" s="1"/>
+    </row>
+    <row r="21" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B21" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M21" s="1"/>
+      <c r="N21" s="1"/>
+      <c r="O21" s="1"/>
+      <c r="P21" s="1"/>
+    </row>
+    <row r="22" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B22" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="I22" s="1"/>
+      <c r="J22" s="1"/>
+      <c r="K22" s="1"/>
+      <c r="L22" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M22" s="1"/>
+      <c r="N22" s="1"/>
+      <c r="O22" s="1"/>
+      <c r="P22" s="1"/>
+    </row>
+    <row r="23" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B23" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1"/>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M23" s="1"/>
+      <c r="N23" s="1"/>
+      <c r="O23" s="1"/>
+      <c r="P23" s="1"/>
+    </row>
+    <row r="24" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B24" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1"/>
+      <c r="K24" s="1"/>
+      <c r="L24" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M24" s="1"/>
+      <c r="N24" s="1"/>
+      <c r="O24" s="1"/>
+      <c r="P24" s="1"/>
+    </row>
+    <row r="25" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B25" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1"/>
+      <c r="K25" s="1"/>
+      <c r="L25" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M25" s="1"/>
+      <c r="N25" s="1"/>
+      <c r="O25" s="1"/>
+      <c r="P25" s="1"/>
+    </row>
+    <row r="26" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B26" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1"/>
+      <c r="K26" s="1"/>
+      <c r="L26" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M26" s="1"/>
+      <c r="N26" s="1"/>
+      <c r="O26" s="1"/>
+      <c r="P26" s="1"/>
+    </row>
+    <row r="27" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B27" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1"/>
+      <c r="K27" s="1"/>
+      <c r="L27" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M27" s="1"/>
+      <c r="N27" s="1"/>
+      <c r="O27" s="1"/>
+      <c r="P27" s="1"/>
+    </row>
+    <row r="28" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B28" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="J28" s="1"/>
+      <c r="K28" s="1"/>
+      <c r="L28" s="1"/>
+      <c r="M28" s="1"/>
+      <c r="N28" s="1"/>
+      <c r="O28" s="1"/>
+      <c r="P28" s="1"/>
+    </row>
+    <row r="29" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B29" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1"/>
+      <c r="K29" s="1"/>
+      <c r="L29" s="1"/>
+      <c r="M29" s="1"/>
+      <c r="N29" s="1"/>
+      <c r="O29" s="1"/>
+      <c r="P29" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="30" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B30" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1"/>
+      <c r="K30" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L30" s="1"/>
+      <c r="M30" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="N30" s="1"/>
+      <c r="O30" s="1"/>
+      <c r="P30" s="1"/>
+    </row>
+    <row r="31" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B31" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1"/>
+      <c r="K31" s="1"/>
+      <c r="L31" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M31" s="1"/>
+      <c r="N31" s="1"/>
+      <c r="O31" s="1"/>
+      <c r="P31" s="1"/>
+    </row>
+    <row r="32" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B32" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
+      <c r="M32" s="1"/>
+      <c r="N32" s="1"/>
+      <c r="O32" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P32" s="1"/>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B33" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+      <c r="J33" s="1"/>
+      <c r="K33" s="1"/>
+      <c r="L33" s="1"/>
+      <c r="M33" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="N33" s="1"/>
+      <c r="O33" s="1"/>
+      <c r="P33" s="1"/>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B34" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+      <c r="J34" s="1"/>
+      <c r="K34" s="1"/>
+      <c r="L34" s="1"/>
+      <c r="M34" s="1"/>
+      <c r="N34" s="1"/>
+      <c r="O34" s="1"/>
+      <c r="P34" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B35" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="I35" s="1"/>
+      <c r="J35" s="1"/>
+      <c r="K35" s="1"/>
+      <c r="L35" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M35" s="1"/>
+      <c r="N35" s="1"/>
+      <c r="O35" s="1"/>
+      <c r="P35" s="1"/>
+    </row>
+    <row r="36" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B36" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
+      <c r="J36" s="1"/>
+      <c r="K36" s="1"/>
+      <c r="L36" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="M36" s="1"/>
+      <c r="N36" s="1"/>
+      <c r="O36" s="1"/>
+      <c r="P36" s="1"/>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B37" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
+      <c r="I37" s="1"/>
+      <c r="J37" s="1"/>
+      <c r="K37" s="1"/>
+      <c r="L37" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="M37" s="1"/>
+      <c r="N37" s="1"/>
+      <c r="O37" s="1"/>
+      <c r="P37" s="1"/>
+    </row>
+    <row r="38" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B38" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="1"/>
+      <c r="J38" s="1"/>
+      <c r="K38" s="1"/>
+      <c r="L38" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="M38" s="1"/>
+      <c r="N38" s="1"/>
+      <c r="O38" s="1"/>
+      <c r="P38" s="1"/>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B39" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
+      <c r="I39" s="1"/>
+      <c r="J39" s="1"/>
+      <c r="K39" s="1"/>
+      <c r="L39" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="M39" s="1"/>
+      <c r="N39" s="1"/>
+      <c r="O39" s="1"/>
+      <c r="P39" s="1"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B40" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="I40" s="1"/>
+      <c r="J40" s="1"/>
+      <c r="K40" s="1"/>
+      <c r="L40" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M40" s="1"/>
+      <c r="N40" s="1"/>
+      <c r="O40" s="1"/>
+      <c r="P40" s="1"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B41" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="F41" s="1"/>
+      <c r="G41" s="1"/>
+      <c r="H41" s="1"/>
+      <c r="I41" s="1"/>
+      <c r="J41" s="1"/>
+      <c r="K41" s="1"/>
+      <c r="L41" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M41" s="1"/>
+      <c r="N41" s="1"/>
+      <c r="O41" s="1"/>
+      <c r="P41" s="1"/>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B42" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="F42" s="1"/>
+      <c r="G42" s="1"/>
+      <c r="H42" s="1"/>
+      <c r="I42" s="1"/>
+      <c r="J42" s="1"/>
+      <c r="K42" s="1"/>
+      <c r="L42" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="M42" s="1"/>
+      <c r="N42" s="1"/>
+      <c r="O42" s="1"/>
+      <c r="P42" s="1"/>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B43" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I43" s="1"/>
+      <c r="J43" s="1"/>
+      <c r="K43" s="1"/>
+      <c r="L43" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M43" s="1"/>
+      <c r="N43" s="1"/>
+      <c r="O43" s="1"/>
+      <c r="P43" s="1"/>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B44" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="F44" s="1"/>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1"/>
+      <c r="I44" s="1"/>
+      <c r="J44" s="1"/>
+      <c r="K44" s="1"/>
+      <c r="L44" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="M44" s="1"/>
+      <c r="N44" s="1"/>
+      <c r="O44" s="1"/>
+      <c r="P44" s="1"/>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B45" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="F45" s="1"/>
+      <c r="G45" s="1"/>
+      <c r="H45" s="1"/>
+      <c r="I45" s="1"/>
+      <c r="J45" s="1"/>
+      <c r="K45" s="1"/>
+      <c r="L45" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="M45" s="1"/>
+      <c r="N45" s="1"/>
+      <c r="O45" s="1"/>
+      <c r="P45" s="1"/>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B46" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="I46" s="1"/>
+      <c r="J46" s="1"/>
+      <c r="K46" s="1"/>
+      <c r="L46" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M46" s="1"/>
+      <c r="N46" s="1"/>
+      <c r="O46" s="1"/>
+      <c r="P46" s="1"/>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B47" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="F47" s="1"/>
+      <c r="G47" s="1"/>
+      <c r="H47" s="1"/>
+      <c r="I47" s="1"/>
+      <c r="J47" s="1"/>
+      <c r="K47" s="1"/>
+      <c r="L47" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="M47" s="1"/>
+      <c r="N47" s="1"/>
+      <c r="O47" s="1"/>
+      <c r="P47" s="1"/>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B48" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="I48" s="1"/>
+      <c r="J48" s="1"/>
+      <c r="K48" s="1"/>
+      <c r="L48" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M48" s="1"/>
+      <c r="N48" s="1"/>
+      <c r="O48" s="1"/>
+      <c r="P48" s="1"/>
+    </row>
+    <row r="49" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B49" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="F49" s="1"/>
+      <c r="G49" s="1"/>
+      <c r="H49" s="1"/>
+      <c r="I49" s="1"/>
+      <c r="J49" s="1"/>
+      <c r="K49" s="1"/>
+      <c r="L49" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="M49" s="1"/>
+      <c r="N49" s="1"/>
+      <c r="O49" s="1"/>
+      <c r="P49" s="1"/>
+    </row>
+    <row r="50" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B50" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="I50" s="1"/>
+      <c r="J50" s="1"/>
+      <c r="K50" s="1"/>
+      <c r="L50" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M50" s="1"/>
+      <c r="N50" s="1"/>
+      <c r="O50" s="1"/>
+      <c r="P50" s="1"/>
+    </row>
+    <row r="51" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B51" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="F51" s="1"/>
+      <c r="G51" s="1"/>
+      <c r="H51" s="1"/>
+      <c r="I51" s="1"/>
+      <c r="J51" s="1"/>
+      <c r="K51" s="1"/>
+      <c r="L51" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M51" s="1"/>
+      <c r="N51" s="1"/>
+      <c r="O51" s="1"/>
+      <c r="P51" s="1"/>
+    </row>
+    <row r="52" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B52" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="F52" s="1"/>
+      <c r="G52" s="1"/>
+      <c r="H52" s="1"/>
+      <c r="I52" s="1"/>
+      <c r="J52" s="1"/>
+      <c r="K52" s="1"/>
+      <c r="L52" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="M52" s="1"/>
+      <c r="N52" s="1"/>
+      <c r="O52" s="1"/>
+      <c r="P52" s="1"/>
+    </row>
+    <row r="53" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B53" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="1"/>
+      <c r="D53" s="1"/>
+      <c r="E53" s="1"/>
+      <c r="F53" s="1"/>
+      <c r="G53" s="1"/>
+      <c r="H53" s="1"/>
+      <c r="I53" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="J53" s="1"/>
+      <c r="K53" s="1"/>
+      <c r="L53" s="1"/>
+      <c r="M53" s="1"/>
+      <c r="N53" s="1"/>
+      <c r="O53" s="1"/>
+      <c r="P53" s="1"/>
+    </row>
+    <row r="54" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B54" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C54" s="1"/>
+      <c r="D54" s="1"/>
+      <c r="E54" s="1"/>
+      <c r="F54" s="1"/>
+      <c r="G54" s="1"/>
+      <c r="H54" s="1"/>
+      <c r="I54" s="1"/>
+      <c r="J54" s="1"/>
+      <c r="K54" s="1"/>
+      <c r="L54" s="1"/>
+      <c r="M54" s="1"/>
+      <c r="N54" s="1"/>
+      <c r="O54" s="1"/>
+      <c r="P54" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="55" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B55" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C55" s="1"/>
+      <c r="D55" s="1"/>
+      <c r="E55" s="1"/>
+      <c r="F55" s="1"/>
+      <c r="G55" s="1"/>
+      <c r="H55" s="1"/>
+      <c r="I55" s="1"/>
+      <c r="J55" s="1"/>
+      <c r="K55" s="1"/>
+      <c r="L55" s="1"/>
+      <c r="M55" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="N55" s="1"/>
+      <c r="O55" s="1"/>
+      <c r="P55" s="1"/>
+    </row>
+    <row r="56" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B56" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C56" s="1"/>
+      <c r="D56" s="1"/>
+      <c r="E56" s="1"/>
+      <c r="F56" s="1"/>
+      <c r="G56" s="1"/>
+      <c r="H56" s="1"/>
+      <c r="I56" s="1"/>
+      <c r="J56" s="1"/>
+      <c r="K56" s="1"/>
+      <c r="L56" s="1"/>
+      <c r="M56" s="1"/>
+      <c r="N56" s="1"/>
+      <c r="O56" s="1"/>
+      <c r="P56" s="1"/>
+    </row>
+    <row r="57" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B57" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="H57" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="I57" s="1"/>
+      <c r="J57" s="1"/>
+      <c r="K57" s="1"/>
+      <c r="L57" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M57" s="1"/>
+      <c r="N57" s="1"/>
+      <c r="O57" s="1"/>
+      <c r="P57" s="1"/>
+    </row>
+    <row r="58" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B58" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="H58" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="I58" s="1"/>
+      <c r="J58" s="1"/>
+      <c r="K58" s="1"/>
+      <c r="L58" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M58" s="1"/>
+      <c r="N58" s="1"/>
+      <c r="O58" s="1"/>
+      <c r="P58" s="1"/>
+    </row>
+    <row r="59" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B59" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="I59" s="1"/>
+      <c r="J59" s="1"/>
+      <c r="K59" s="1"/>
+      <c r="L59" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M59" s="1"/>
+      <c r="N59" s="1"/>
+      <c r="O59" s="1"/>
+      <c r="P59" s="1"/>
+    </row>
+    <row r="60" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B60" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="I60" s="1"/>
+      <c r="J60" s="1"/>
+      <c r="K60" s="1"/>
+      <c r="L60" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M60" s="1"/>
+      <c r="N60" s="1"/>
+      <c r="O60" s="1"/>
+      <c r="P60" s="1"/>
+    </row>
+    <row r="61" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B61" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="F61" s="1"/>
+      <c r="G61" s="1"/>
+      <c r="H61" s="1"/>
+      <c r="I61" s="1"/>
+      <c r="J61" s="1"/>
+      <c r="K61" s="1"/>
+      <c r="L61" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="M61" s="1"/>
+      <c r="N61" s="1"/>
+      <c r="O61" s="1"/>
+      <c r="P61" s="1"/>
+    </row>
+    <row r="62" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B62" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="J62" s="1"/>
+      <c r="K62" s="1"/>
+      <c r="L62" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="M62" s="1"/>
+      <c r="N62" s="1"/>
+      <c r="O62" s="1"/>
+      <c r="P62" s="1"/>
+    </row>
+    <row r="63" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B63" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="F63" s="1"/>
+      <c r="G63" s="1"/>
+      <c r="H63" s="1"/>
+      <c r="I63" s="1"/>
+      <c r="J63" s="1"/>
+      <c r="K63" s="1"/>
+      <c r="L63" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="M63" s="1"/>
+      <c r="N63" s="1"/>
+      <c r="O63" s="1"/>
+      <c r="P63" s="1"/>
+    </row>
+    <row r="64" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B64" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="F64" s="1"/>
+      <c r="G64" s="1"/>
+      <c r="H64" s="1"/>
+      <c r="I64" s="1"/>
+      <c r="J64" s="1"/>
+      <c r="K64" s="1"/>
+      <c r="L64" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="M64" s="1"/>
+      <c r="N64" s="1"/>
+      <c r="O64" s="1"/>
+      <c r="P64" s="1"/>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B65" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="F65" s="1"/>
+      <c r="G65" s="1"/>
+      <c r="H65" s="1"/>
+      <c r="I65" s="1"/>
+      <c r="J65" s="1"/>
+      <c r="K65" s="1"/>
+      <c r="L65" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="M65" s="1"/>
+      <c r="N65" s="1"/>
+      <c r="O65" s="1"/>
+      <c r="P65" s="1"/>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B66" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="J66" s="1"/>
+      <c r="K66" s="1"/>
+      <c r="L66" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="M66" s="1"/>
+      <c r="N66" s="1"/>
+      <c r="O66" s="1"/>
+      <c r="P66" s="1"/>
+    </row>
+    <row r="67" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B67" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="H67" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="I67" s="1"/>
+      <c r="J67" s="1"/>
+      <c r="K67" s="1"/>
+      <c r="L67" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M67" s="1"/>
+      <c r="N67" s="1"/>
+      <c r="O67" s="1"/>
+      <c r="P67" s="1"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B68" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="H68" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="I68" s="1"/>
+      <c r="J68" s="1"/>
+      <c r="K68" s="1"/>
+      <c r="L68" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M68" s="1"/>
+      <c r="N68" s="1"/>
+      <c r="O68" s="1"/>
+      <c r="P68" s="1"/>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B69" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="H69" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="I69" s="1"/>
+      <c r="J69" s="1"/>
+      <c r="K69" s="1"/>
+      <c r="L69" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M69" s="1"/>
+      <c r="N69" s="1"/>
+      <c r="O69" s="1"/>
+      <c r="P69" s="1"/>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B70" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="J70" s="1"/>
+      <c r="K70" s="1"/>
+      <c r="L70" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="M70" s="1"/>
+      <c r="N70" s="1"/>
+      <c r="O70" s="1"/>
+      <c r="P70" s="1"/>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B71" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="F71" s="1"/>
+      <c r="G71" s="1"/>
+      <c r="H71" s="1"/>
+      <c r="I71" s="1"/>
+      <c r="J71" s="1"/>
+      <c r="K71" s="1"/>
+      <c r="L71" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="M71" s="1"/>
+      <c r="N71" s="1"/>
+      <c r="O71" s="1"/>
+      <c r="P71" s="1"/>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B72" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="H72" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="I72" s="1"/>
+      <c r="J72" s="1"/>
+      <c r="K72" s="1"/>
+      <c r="L72" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M72" s="1"/>
+      <c r="N72" s="1"/>
+      <c r="O72" s="1"/>
+      <c r="P72" s="1"/>
+    </row>
+    <row r="73" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B73" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C73" s="1"/>
+      <c r="D73" s="1"/>
+      <c r="E73" s="1"/>
+      <c r="F73" s="1"/>
+      <c r="G73" s="1"/>
+      <c r="H73" s="1"/>
+      <c r="I73" s="1"/>
+      <c r="J73" s="1"/>
+      <c r="K73" s="1"/>
+      <c r="L73" s="1"/>
+      <c r="M73" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="N73" s="1"/>
+      <c r="O73" s="1"/>
+      <c r="P73" s="1"/>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B74" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C74" s="1"/>
+      <c r="D74" s="1"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
+      <c r="J74" s="1"/>
+      <c r="K74" s="1"/>
+      <c r="L74" s="1"/>
+      <c r="M74" s="1"/>
+      <c r="N74" s="1"/>
+      <c r="O74" s="1"/>
+      <c r="P74" s="1"/>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B75" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C75" s="1"/>
+      <c r="D75" s="1"/>
+      <c r="E75" s="1"/>
+      <c r="F75" s="1"/>
+      <c r="G75" s="1"/>
+      <c r="H75" s="1"/>
+      <c r="I75" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="J75" s="1"/>
+      <c r="K75" s="1"/>
+      <c r="L75" s="1"/>
+      <c r="M75" s="1"/>
+      <c r="N75" s="1"/>
+      <c r="O75" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P75" s="1"/>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B76" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C76" s="1"/>
+      <c r="D76" s="1"/>
+      <c r="E76" s="1"/>
+      <c r="F76" s="1"/>
+      <c r="G76" s="1"/>
+      <c r="H76" s="1"/>
+      <c r="I76" s="1"/>
+      <c r="J76" s="1"/>
+      <c r="K76" s="1"/>
+      <c r="L76" s="1"/>
+      <c r="M76" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="N76" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="O76" s="1"/>
+      <c r="P76" s="1"/>
+    </row>
+    <row r="77" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B77" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C77" s="1"/>
+      <c r="D77" s="1"/>
+      <c r="E77" s="1"/>
+      <c r="F77" s="1"/>
+      <c r="G77" s="1"/>
+      <c r="H77" s="1"/>
+      <c r="I77" s="1"/>
+      <c r="J77" s="1"/>
+      <c r="K77" s="1"/>
+      <c r="L77" s="1"/>
+      <c r="M77" s="1"/>
+      <c r="N77" s="1"/>
+      <c r="O77" s="1"/>
+      <c r="P77" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="78" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B78" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G78" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H78" t="s">
+        <v>103</v>
+      </c>
+      <c r="I78" s="1"/>
+      <c r="J78" s="1"/>
+      <c r="K78" s="1"/>
+      <c r="L78" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M78" s="1"/>
+      <c r="N78" s="1"/>
+      <c r="O78" s="1"/>
+      <c r="P78" s="1"/>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B79" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H79" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="I79" s="1"/>
+      <c r="J79" s="1"/>
+      <c r="K79" s="1"/>
+      <c r="L79" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M79" s="1"/>
+      <c r="N79" s="1"/>
+      <c r="O79" s="1"/>
+      <c r="P79" s="1"/>
+    </row>
+    <row r="80" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B80" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D80" t="s">
+        <v>99</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F80" s="1"/>
+      <c r="L80" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B81" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G81" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="H81" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="I81" s="1"/>
+      <c r="J81" s="1"/>
+      <c r="K81" s="1"/>
+      <c r="L81" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M81" s="1"/>
+      <c r="N81" s="1"/>
+      <c r="O81" s="1"/>
+      <c r="P81" s="1"/>
+    </row>
+    <row r="82" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B82" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G82" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H82" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I82" s="1"/>
+      <c r="J82" s="1"/>
+      <c r="K82" s="1"/>
+      <c r="L82" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M82" s="1"/>
+      <c r="N82" s="1"/>
+      <c r="O82" s="1"/>
+      <c r="P82" s="1"/>
+    </row>
+    <row r="83" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B83" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F83" s="1"/>
+      <c r="G83" s="1"/>
+      <c r="H83" s="1"/>
+      <c r="I83" s="1"/>
+      <c r="J83" s="1"/>
+      <c r="K83" s="1"/>
+      <c r="L83" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="M83" s="1"/>
+      <c r="N83" s="1"/>
+      <c r="O83" s="1"/>
+      <c r="P83" s="1"/>
+    </row>
+    <row r="84" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B84" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="85" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B85" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F85" t="s">
+        <v>52</v>
+      </c>
+      <c r="I85" s="1"/>
+      <c r="J85" s="1"/>
+      <c r="K85" s="1"/>
+      <c r="L85" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M85" s="1"/>
+      <c r="N85" s="1"/>
+      <c r="O85" s="1"/>
+      <c r="P85" s="1"/>
+    </row>
+    <row r="86" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B86" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D86" t="s">
+        <v>84</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G86" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H86" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="L86">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B87" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D87" t="s">
+        <v>81</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="L87">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B88" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D88" t="s">
+        <v>79</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="L88">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B89" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G89" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H89" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="I89" s="1"/>
+      <c r="J89" s="1"/>
+      <c r="K89" s="1"/>
+      <c r="L89" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M89" s="1"/>
+      <c r="N89" s="1"/>
+      <c r="O89" s="1"/>
+      <c r="P89" s="1"/>
+    </row>
+    <row r="90" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B90" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F90" s="1"/>
+      <c r="G90" s="1"/>
+      <c r="H90" s="1"/>
+      <c r="I90" s="1"/>
+      <c r="J90" s="1"/>
+      <c r="K90" s="1"/>
+      <c r="L90" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M90" s="1"/>
+      <c r="N90" s="1"/>
+      <c r="O90" s="1"/>
+      <c r="P90" s="1"/>
+    </row>
+    <row r="91" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B91" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G91" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H91" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="I91" s="1"/>
+      <c r="J91" s="1"/>
+      <c r="K91" s="1"/>
+      <c r="L91" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M91" s="1"/>
+      <c r="N91" s="1"/>
+      <c r="O91" s="1"/>
+      <c r="P91" s="1"/>
+    </row>
+    <row r="92" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B92" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G92" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H92" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="I92" s="1"/>
+      <c r="J92" s="1"/>
+      <c r="K92" s="1"/>
+      <c r="L92" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M92" s="1"/>
+      <c r="N92" s="1"/>
+      <c r="O92" s="1"/>
+      <c r="P92" s="1"/>
+    </row>
+    <row r="93" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B93" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F93" t="s">
+        <v>52</v>
+      </c>
+      <c r="I93" s="1"/>
+      <c r="J93" s="1"/>
+      <c r="K93" s="1"/>
+      <c r="L93" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M93" s="1"/>
+      <c r="N93" s="1"/>
+      <c r="O93" s="1"/>
+      <c r="P93" s="1"/>
+    </row>
+    <row r="94" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B94" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F94" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="G94" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="H94" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I94" s="1"/>
+      <c r="J94" s="1"/>
+      <c r="K94" s="1"/>
+      <c r="L94" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M94" s="1"/>
+      <c r="N94" s="1"/>
+      <c r="O94" s="1"/>
+      <c r="P94" s="1"/>
+    </row>
+    <row r="95" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B95" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F95" s="3"/>
+      <c r="G95" s="3"/>
+      <c r="H95" s="2"/>
+      <c r="I95" s="1"/>
+      <c r="J95" s="1"/>
+      <c r="K95" s="1"/>
+      <c r="L95" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M95" s="1"/>
+      <c r="N95" s="1"/>
+      <c r="O95" s="1"/>
+      <c r="P95" s="1"/>
+    </row>
+    <row r="96" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B96" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C96" s="1"/>
+      <c r="D96" s="1"/>
+      <c r="E96" s="1"/>
+      <c r="F96" s="1"/>
+      <c r="G96" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H96" s="1"/>
+      <c r="I96" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J96" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="K96" s="1"/>
+      <c r="L96" s="1"/>
+      <c r="M96" s="1"/>
+      <c r="N96" s="1"/>
+      <c r="O96" s="1"/>
+      <c r="P96" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="97" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B97" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F97" t="s">
+        <v>52</v>
+      </c>
+      <c r="I97" s="1"/>
+      <c r="J97" s="1"/>
+      <c r="K97" s="1"/>
+      <c r="L97" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M97" s="1"/>
+      <c r="N97" s="1"/>
+      <c r="O97" s="1"/>
+      <c r="P97" s="1"/>
+    </row>
+    <row r="98" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B98" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G98" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H98" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I98" s="1"/>
+      <c r="J98" s="1"/>
+      <c r="K98" s="1"/>
+      <c r="L98" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M98" s="1"/>
+      <c r="N98" s="1"/>
+      <c r="O98" s="1"/>
+      <c r="P98" s="1"/>
+    </row>
+    <row r="99" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B99" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F99" s="1"/>
+      <c r="G99" s="1"/>
+      <c r="H99" s="1"/>
+      <c r="I99" s="1"/>
+      <c r="J99" s="1"/>
+      <c r="K99" s="1"/>
+      <c r="L99" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M99" s="1"/>
+      <c r="N99" s="1"/>
+      <c r="O99" s="1"/>
+      <c r="P99" s="1"/>
+    </row>
+    <row r="100" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B100" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F100" s="1"/>
+      <c r="G100" s="1"/>
+      <c r="H100" s="1"/>
+      <c r="I100" s="1"/>
+      <c r="J100" s="1"/>
+      <c r="K100" s="1"/>
+      <c r="L100" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M100" s="1"/>
+      <c r="N100" s="1"/>
+      <c r="O100" s="1"/>
+      <c r="P100" s="1"/>
+    </row>
+    <row r="101" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B101" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I101" s="1"/>
+      <c r="J101" s="1"/>
+      <c r="K101" s="1"/>
+      <c r="L101" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M101" s="1"/>
+      <c r="N101" s="1"/>
+      <c r="O101" s="1"/>
+      <c r="P101" s="1"/>
+    </row>
+    <row r="102" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B102" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G102" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H102" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="I102" s="1"/>
+      <c r="J102" s="1"/>
+      <c r="K102" s="1"/>
+      <c r="L102" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M102" s="1"/>
+      <c r="N102" s="1"/>
+      <c r="O102" s="1"/>
+      <c r="P102" s="1"/>
+    </row>
+    <row r="103" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B103" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F103" s="1"/>
+      <c r="G103" s="1"/>
+      <c r="H103" s="1"/>
+      <c r="I103" s="1"/>
+      <c r="J103" s="1"/>
+      <c r="K103" s="1"/>
+      <c r="L103" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M103" s="1"/>
+      <c r="N103" s="1"/>
+      <c r="O103" s="1"/>
+      <c r="P103" s="1"/>
+    </row>
+    <row r="104" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B104" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F104" s="1"/>
+      <c r="G104" s="1"/>
+      <c r="H104" s="1"/>
+      <c r="I104" s="1"/>
+      <c r="J104" s="1"/>
+      <c r="K104" s="1"/>
+      <c r="L104" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M104" s="1"/>
+      <c r="N104" s="1"/>
+      <c r="O104" s="1"/>
+      <c r="P104" s="1"/>
+    </row>
+    <row r="105" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B105" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C105" s="1"/>
+      <c r="D105" s="1"/>
+      <c r="E105" s="1"/>
+      <c r="F105" s="1"/>
+      <c r="G105" s="1"/>
+      <c r="H105" s="1"/>
+      <c r="I105" s="1"/>
+      <c r="J105" s="1"/>
+      <c r="K105" s="1"/>
+      <c r="L105" s="1"/>
+      <c r="M105" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N105" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="O105" s="1"/>
+      <c r="P105" s="1"/>
+    </row>
+    <row r="106" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B106" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F106" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G106" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H106" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I106" s="1"/>
+      <c r="J106" s="1"/>
+      <c r="K106" s="1"/>
+      <c r="L106" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M106" s="1"/>
+      <c r="N106" s="1"/>
+      <c r="O106" s="1"/>
+      <c r="P106" s="1"/>
+    </row>
+    <row r="107" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B107" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F107" s="3"/>
+      <c r="G107" s="3"/>
+      <c r="H107" s="4"/>
+      <c r="I107" s="1"/>
+      <c r="J107" s="1"/>
+      <c r="K107" s="1"/>
+      <c r="L107" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M107" s="1"/>
+      <c r="N107" s="1"/>
+      <c r="O107" s="1"/>
+      <c r="P107" s="1"/>
+    </row>
+    <row r="108" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B108" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G108" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H108" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I108" s="1"/>
+      <c r="J108" s="1"/>
+      <c r="K108" s="1"/>
+      <c r="L108" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M108" s="1"/>
+      <c r="N108" s="1"/>
+      <c r="O108" s="1"/>
+      <c r="P108" s="1"/>
+    </row>
+    <row r="109" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B109" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F109" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G109" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H109" t="s">
+        <v>19</v>
+      </c>
+      <c r="I109" s="1"/>
+      <c r="J109" s="1"/>
+      <c r="K109" s="1"/>
+      <c r="L109" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M109" s="1"/>
+      <c r="N109" s="1"/>
+      <c r="O109" s="1"/>
+      <c r="P109" s="1"/>
+    </row>
+    <row r="110" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B110" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F110" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G110" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="I110" s="1"/>
+      <c r="J110" s="1"/>
+      <c r="K110" s="1"/>
+      <c r="L110" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M110" s="1"/>
+      <c r="N110" s="1"/>
+      <c r="O110" s="1"/>
+      <c r="P110" s="1"/>
+    </row>
+    <row r="111" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B111" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E111" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F111" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G111" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H111" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I111" s="1"/>
+      <c r="J111" s="1"/>
+      <c r="K111" s="1"/>
+      <c r="L111" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M111" s="1"/>
+      <c r="N111" s="1"/>
+      <c r="O111" s="1"/>
+      <c r="P111" s="1"/>
+    </row>
+    <row r="112" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B112" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F112" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G112" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="I112" s="1"/>
+      <c r="J112" s="1"/>
+      <c r="K112" s="1"/>
+      <c r="L112" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M112" s="1"/>
+      <c r="N112" s="1"/>
+      <c r="O112" s="1"/>
+      <c r="P112" s="1"/>
+    </row>
+    <row r="113" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B113" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C113" s="1"/>
+      <c r="D113" s="1"/>
+      <c r="E113" s="1"/>
+      <c r="F113" s="1"/>
+      <c r="G113" s="1"/>
+      <c r="H113" s="1"/>
+      <c r="I113" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J113" s="1"/>
+      <c r="K113" s="1"/>
+      <c r="L113" s="1"/>
+      <c r="M113" s="1"/>
+      <c r="N113" s="1"/>
+      <c r="O113" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P113" s="1"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7C8F638-A372-42C6-A1FE-F949BD85ECC5}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>

--- a/resource/Script/script_InertiaLucis.xlsx
+++ b/resource/Script/script_InertiaLucis.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\usosctheater\resource\Script\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF09E5A9-4EA2-420E-B8C8-9F356C2BB142}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A20C6C6-B1F2-46A4-BED6-91D39D0E7C13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="26010" windowHeight="20985" activeTab="2" xr2:uid="{12160F34-6A21-4287-85A5-86880D8D3A1A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="2" xr2:uid="{12160F34-6A21-4287-85A5-86880D8D3A1A}"/>
   </bookViews>
   <sheets>
     <sheet name="Scene1" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2171" uniqueCount="680">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2291" uniqueCount="785">
   <si>
     <t>se_trans_out|se_trans_in</t>
   </si>
@@ -1794,10 +1794,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>wait2 face_serious lip_surp</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>뭠까?</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -1822,10 +1818,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>skill3 face_serious lip_smile</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>저 자신은 어디서 오는 지 몰라.</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -1902,10 +1894,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>serious face_smile</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>응, 부탁할게.</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -1974,10 +1962,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>바보 같아.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>팬</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -2038,18 +2022,10 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>smile1 lip_bitter_smile</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>바보가 옮아 버렸잖아,</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>anger1 face_smile lip_sad</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>SE</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -2226,10 +2202,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>anger1 face_jito_lip_smile</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>뭐, 좋은 게 좋은 거려나…</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -2298,10 +2270,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>anger2 face_serious lip_smile</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>가버렸슴다.</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -2311,6 +2279,380 @@
   </si>
   <si>
     <t>아사히</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>bg_runninTrack_1</t>
+  </si>
+  <si>
+    <t>bg_runninTrack_1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>BG</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>se_zawa</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>loop</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>BGM</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>se_kansei</t>
+  </si>
+  <si>
+    <t>S003001</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>S003003</t>
+  </si>
+  <si>
+    <t>S003002</t>
+  </si>
+  <si>
+    <t>S003004</t>
+  </si>
+  <si>
+    <t>S003005</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>S003006</t>
+  </si>
+  <si>
+    <t>S003007</t>
+  </si>
+  <si>
+    <t>S003008</t>
+  </si>
+  <si>
+    <t>S003009</t>
+  </si>
+  <si>
+    <t>S003010</t>
+  </si>
+  <si>
+    <t>S003011</t>
+  </si>
+  <si>
+    <t>S003012</t>
+  </si>
+  <si>
+    <t>S003013</t>
+  </si>
+  <si>
+    <t>S003014</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>S003034</t>
+  </si>
+  <si>
+    <t>S003015</t>
+  </si>
+  <si>
+    <t>S003016</t>
+  </si>
+  <si>
+    <t>S003017</t>
+  </si>
+  <si>
+    <t>S003018</t>
+  </si>
+  <si>
+    <t>S003019</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>S003039</t>
+  </si>
+  <si>
+    <t>S003020</t>
+  </si>
+  <si>
+    <t>S003021</t>
+  </si>
+  <si>
+    <t>S003022</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>S003023</t>
+  </si>
+  <si>
+    <t>S003024</t>
+  </si>
+  <si>
+    <t>S003025</t>
+  </si>
+  <si>
+    <t>S003026</t>
+  </si>
+  <si>
+    <t>S003027</t>
+  </si>
+  <si>
+    <t>S003028</t>
+  </si>
+  <si>
+    <t>S003029</t>
+  </si>
+  <si>
+    <t>S003030</t>
+  </si>
+  <si>
+    <t>S003031</t>
+  </si>
+  <si>
+    <t>S003032</t>
+  </si>
+  <si>
+    <t>S003033</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>S003035</t>
+  </si>
+  <si>
+    <t>S003036</t>
+  </si>
+  <si>
+    <t>S003037</t>
+  </si>
+  <si>
+    <t>S003038</t>
+  </si>
+  <si>
+    <t>S003040</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>S003041</t>
+  </si>
+  <si>
+    <t>S003043</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>S003044</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>S003045</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>S003046</t>
+  </si>
+  <si>
+    <t>S003047</t>
+  </si>
+  <si>
+    <t>S003048</t>
+  </si>
+  <si>
+    <t>S003049</t>
+  </si>
+  <si>
+    <t>S003050</t>
+  </si>
+  <si>
+    <t>S003051</t>
+  </si>
+  <si>
+    <t>S003053</t>
+  </si>
+  <si>
+    <t>S003052</t>
+  </si>
+  <si>
+    <t>S003054</t>
+  </si>
+  <si>
+    <t>S003055</t>
+  </si>
+  <si>
+    <t>S003056</t>
+  </si>
+  <si>
+    <t>S003057</t>
+  </si>
+  <si>
+    <t>S003058</t>
+  </si>
+  <si>
+    <t>S003059</t>
+  </si>
+  <si>
+    <t>S003060</t>
+  </si>
+  <si>
+    <t>S003061</t>
+  </si>
+  <si>
+    <t>S003062</t>
+  </si>
+  <si>
+    <t>S003063</t>
+  </si>
+  <si>
+    <t>S003064</t>
+  </si>
+  <si>
+    <t>S003065</t>
+  </si>
+  <si>
+    <t>S003066</t>
+  </si>
+  <si>
+    <t>S003067</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>S003068</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>S003069</t>
+  </si>
+  <si>
+    <t>S003070</t>
+  </si>
+  <si>
+    <t>S003071</t>
+  </si>
+  <si>
+    <t>S003072</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>S003073</t>
+  </si>
+  <si>
+    <t>S003074</t>
+  </si>
+  <si>
+    <t>S003075</t>
+  </si>
+  <si>
+    <t>S003076</t>
+  </si>
+  <si>
+    <t>S003077</t>
+  </si>
+  <si>
+    <t>S003078</t>
+  </si>
+  <si>
+    <t>S003079</t>
+  </si>
+  <si>
+    <t>S003080</t>
+  </si>
+  <si>
+    <t>S003081</t>
+  </si>
+  <si>
+    <t>S003082</t>
+  </si>
+  <si>
+    <t>S003083</t>
+  </si>
+  <si>
+    <t>S003084</t>
+  </si>
+  <si>
+    <t>S003085</t>
+  </si>
+  <si>
+    <t>S003086</t>
+  </si>
+  <si>
+    <t>S003087</t>
+  </si>
+  <si>
+    <t>S003088</t>
+  </si>
+  <si>
+    <t>S003089</t>
+  </si>
+  <si>
+    <t>S003090</t>
+  </si>
+  <si>
+    <t>S003091</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>S003092</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>S003093</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>S003042</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>anger3 face_serious lip_sad</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>bgm_101</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>bgm_121</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>bgm_80</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>… 바보 같아.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>스트레이라이트의 팬</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>shrug2 face_bitter_smile lip_bitter_smile</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>serious face_smile1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>wait2 face_wait lip_surp</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>skill1 face_wait lip_surp</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>skill1 face_serious lip_surp</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>anger1 face_jito lip_smile</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>anger2 face_serious lip_smile1</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -2318,7 +2660,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="14"/>
       <color theme="1"/>
@@ -2360,15 +2702,8 @@
       <family val="2"/>
       <charset val="129"/>
     </font>
-    <font>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="Yu Gothic"/>
-      <family val="3"/>
-      <charset val="128"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2390,6 +2725,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2434,7 +2775,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2462,10 +2803,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2522,7 +2860,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{D176A707-5286-406D-AE81-034E45D172BC}" name="표1_3" displayName="표1_3" ref="B2:P169" totalsRowShown="0" headerRowDxfId="2" headerRowCellStyle="HeadLine">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{D176A707-5286-406D-AE81-034E45D172BC}" name="표1_3" displayName="표1_3" ref="B2:P169" totalsRowShown="0" headerRowDxfId="0" headerRowCellStyle="HeadLine">
   <autoFilter ref="B2:P169" xr:uid="{160FF696-8FC2-44DF-96A2-501D4731471F}"/>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{482BF108-9D0C-4BDE-AA5C-ABAFDC442673}" name="Type"/>
@@ -2546,8 +2884,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{A67FC043-6C28-4372-A869-A8CE73B8F803}" name="표1_34" displayName="표1_34" ref="B2:P164" totalsRowShown="0" headerRowDxfId="0" headerRowCellStyle="HeadLine">
-  <autoFilter ref="B2:P164" xr:uid="{160FF696-8FC2-44DF-96A2-501D4731471F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{A67FC043-6C28-4372-A869-A8CE73B8F803}" name="표1_34" displayName="표1_34" ref="B2:P171" totalsRowShown="0" headerRowDxfId="2" headerRowCellStyle="HeadLine">
+  <autoFilter ref="B2:P171" xr:uid="{160FF696-8FC2-44DF-96A2-501D4731471F}"/>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{3A542181-8544-449B-BB33-D6B10506AD66}" name="Type"/>
     <tableColumn id="2" xr3:uid="{2D8F5C8D-CA18-4393-8E85-311F4810BDFD}" name="Name"/>
@@ -10674,27 +11012,27 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE4D321B-C73D-4912-B6FF-462FE2A5AF56}">
-  <dimension ref="A2:P164"/>
+  <dimension ref="A2:P171"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="11.1640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.08203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="66.4140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.08203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="25.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.08203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.58203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.5" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.4140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.33203125" customWidth="1"/>
+    <col min="7" max="7" width="12.33203125" customWidth="1"/>
+    <col min="8" max="8" width="25.6640625" customWidth="1"/>
+    <col min="9" max="9" width="10.33203125" customWidth="1"/>
+    <col min="10" max="10" width="10.08203125" customWidth="1"/>
+    <col min="11" max="11" width="12.58203125" customWidth="1"/>
+    <col min="12" max="12" width="16.5" customWidth="1"/>
+    <col min="13" max="13" width="13.4140625" customWidth="1"/>
+    <col min="14" max="14" width="11.6640625" customWidth="1"/>
+    <col min="15" max="15" width="20.33203125" customWidth="1"/>
     <col min="16" max="16" width="15.58203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B2" s="7" t="s">
         <v>263</v>
       </c>
@@ -10741,8 +11079,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A3" s="8"/>
+    <row r="3" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>59</v>
       </c>
@@ -10763,8 +11100,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A4" s="8"/>
+    <row r="4" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
         <v>108</v>
       </c>
@@ -10778,14 +11114,16 @@
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
+      <c r="M4" s="1" t="s">
+        <v>773</v>
+      </c>
       <c r="N4" s="1" t="s">
-        <v>265</v>
+        <v>106</v>
       </c>
       <c r="O4" s="1"/>
       <c r="P4" s="1"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
         <v>547</v>
       </c>
@@ -10806,7 +11144,7 @@
       <c r="O5" s="1"/>
       <c r="P5" s="1"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
         <v>10</v>
       </c>
@@ -10816,7 +11154,9 @@
       <c r="D6" s="1" t="s">
         <v>549</v>
       </c>
-      <c r="E6" s="1"/>
+      <c r="E6" s="1" t="s">
+        <v>679</v>
+      </c>
       <c r="F6" s="1" t="s">
         <v>294</v>
       </c>
@@ -10837,8 +11177,7 @@
       <c r="O6" s="1"/>
       <c r="P6" s="1"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A7" s="8"/>
+    <row r="7" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
         <v>10</v>
       </c>
@@ -10846,17 +11185,19 @@
         <v>9</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>551</v>
-      </c>
-      <c r="E7" s="1"/>
+        <v>550</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>681</v>
+      </c>
       <c r="F7" s="1" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>122</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>550</v>
+        <v>780</v>
       </c>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
@@ -10869,7 +11210,7 @@
       <c r="O7" s="1"/>
       <c r="P7" s="1"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
         <v>10</v>
       </c>
@@ -10877,9 +11218,11 @@
         <v>16</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>552</v>
-      </c>
-      <c r="E8" s="1"/>
+        <v>551</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>680</v>
+      </c>
       <c r="F8" s="1" t="s">
         <v>294</v>
       </c>
@@ -10887,7 +11230,7 @@
         <v>12</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
@@ -10900,7 +11243,7 @@
       <c r="O8" s="1"/>
       <c r="P8" s="1"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B9" s="1" t="s">
         <v>10</v>
       </c>
@@ -10908,9 +11251,11 @@
         <v>9</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>555</v>
-      </c>
-      <c r="E9" s="1"/>
+        <v>554</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>682</v>
+      </c>
       <c r="F9" s="1" t="s">
         <v>52</v>
       </c>
@@ -10927,7 +11272,7 @@
       <c r="O9" s="1"/>
       <c r="P9" s="1"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B10" s="1" t="s">
         <v>547</v>
       </c>
@@ -10940,7 +11285,7 @@
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
@@ -10948,7 +11293,7 @@
       <c r="O10" s="1"/>
       <c r="P10" s="1"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B11" s="1" t="s">
         <v>10</v>
       </c>
@@ -10956,17 +11301,19 @@
         <v>9</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>556</v>
-      </c>
-      <c r="E11" s="1"/>
+        <v>555</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>683</v>
+      </c>
       <c r="F11" s="1" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>122</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>557</v>
+        <v>781</v>
       </c>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
@@ -10979,7 +11326,7 @@
       <c r="O11" s="1"/>
       <c r="P11" s="1"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B12" s="1" t="s">
         <v>10</v>
       </c>
@@ -10987,9 +11334,11 @@
         <v>16</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>558</v>
-      </c>
-      <c r="E12" s="1"/>
+        <v>556</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>684</v>
+      </c>
       <c r="F12" s="1" t="s">
         <v>294</v>
       </c>
@@ -10997,7 +11346,7 @@
         <v>12</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>526</v>
+        <v>778</v>
       </c>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
@@ -11010,8 +11359,7 @@
       <c r="O12" s="1"/>
       <c r="P12" s="1"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A13" s="8"/>
+    <row r="13" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B13" s="1" t="s">
         <v>10</v>
       </c>
@@ -11019,17 +11367,19 @@
         <v>24</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>562</v>
-      </c>
-      <c r="E13" s="1"/>
+        <v>560</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>685</v>
+      </c>
       <c r="F13" s="1" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H13" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
@@ -11042,7 +11392,7 @@
       <c r="O13" s="1"/>
       <c r="P13" s="1"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B14" s="1" t="s">
         <v>10</v>
       </c>
@@ -11050,9 +11400,11 @@
         <v>24</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>563</v>
-      </c>
-      <c r="E14" s="1"/>
+        <v>561</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>686</v>
+      </c>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
       <c r="I14" s="1"/>
@@ -11066,7 +11418,7 @@
       <c r="O14" s="1"/>
       <c r="P14" s="1"/>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B15" s="1" t="s">
         <v>10</v>
       </c>
@@ -11074,9 +11426,11 @@
         <v>16</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>564</v>
-      </c>
-      <c r="E15" s="1"/>
+        <v>562</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>687</v>
+      </c>
       <c r="F15" s="1" t="s">
         <v>294</v>
       </c>
@@ -11084,7 +11438,7 @@
         <v>12</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
@@ -11097,7 +11451,7 @@
       <c r="O15" s="1"/>
       <c r="P15" s="1"/>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B16" s="1" t="s">
         <v>10</v>
       </c>
@@ -11105,12 +11459,20 @@
         <v>16</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>566</v>
-      </c>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
+        <v>564</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>772</v>
+      </c>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
@@ -11130,9 +11492,11 @@
         <v>16</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>567</v>
-      </c>
-      <c r="E17" s="1"/>
+        <v>565</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>689</v>
+      </c>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
@@ -11155,17 +11519,19 @@
         <v>24</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>568</v>
-      </c>
-      <c r="E18" s="1"/>
+        <v>566</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>690</v>
+      </c>
       <c r="F18" s="1" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H18" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
@@ -11186,9 +11552,11 @@
         <v>16</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>570</v>
-      </c>
-      <c r="E19" s="1"/>
+        <v>568</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>691</v>
+      </c>
       <c r="F19" s="1" t="s">
         <v>294</v>
       </c>
@@ -11196,7 +11564,7 @@
         <v>12</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
@@ -11286,9 +11654,11 @@
         <v>16</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>572</v>
-      </c>
-      <c r="E23" s="1"/>
+        <v>570</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>692</v>
+      </c>
       <c r="F23" s="1" t="s">
         <v>294</v>
       </c>
@@ -11296,7 +11666,7 @@
         <v>12</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
@@ -11317,9 +11687,11 @@
         <v>9</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>574</v>
-      </c>
-      <c r="E24" s="1"/>
+        <v>572</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>694</v>
+      </c>
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
@@ -11342,9 +11714,11 @@
         <v>16</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>575</v>
-      </c>
-      <c r="E25" s="1"/>
+        <v>573</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>695</v>
+      </c>
       <c r="F25" s="1" t="s">
         <v>294</v>
       </c>
@@ -11373,17 +11747,19 @@
         <v>24</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>576</v>
-      </c>
-      <c r="E26" s="1"/>
+        <v>574</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>696</v>
+      </c>
       <c r="F26" s="1" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>5</v>
       </c>
       <c r="H26" t="s">
-        <v>577</v>
+        <v>779</v>
       </c>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
@@ -11404,9 +11780,11 @@
         <v>16</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>578</v>
-      </c>
-      <c r="E27" s="1"/>
+        <v>575</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>697</v>
+      </c>
       <c r="F27" s="1" t="s">
         <v>294</v>
       </c>
@@ -11429,7 +11807,7 @@
     </row>
     <row r="28" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B28" s="1" t="s">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
@@ -11437,20 +11815,22 @@
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
-      <c r="I28" s="1" t="s">
-        <v>154</v>
-      </c>
+      <c r="I28" s="1"/>
       <c r="J28" s="1"/>
       <c r="K28" s="1"/>
       <c r="L28" s="1"/>
-      <c r="M28" s="1"/>
-      <c r="N28" s="1"/>
+      <c r="M28" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="N28" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="O28" s="1"/>
       <c r="P28" s="1"/>
     </row>
     <row r="29" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B29" s="1" t="s">
-        <v>59</v>
+        <v>2</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
@@ -11458,27 +11838,23 @@
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
+      <c r="I29" s="1" t="s">
+        <v>154</v>
+      </c>
       <c r="J29" s="1"/>
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
       <c r="N29" s="1"/>
       <c r="O29" s="1"/>
-      <c r="P29" s="1" t="s">
-        <v>546</v>
-      </c>
+      <c r="P29" s="1"/>
     </row>
     <row r="30" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B30" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>579</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
@@ -11486,34 +11862,30 @@
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
-      <c r="L30" s="1" t="s">
-        <v>3</v>
-      </c>
+      <c r="L30" s="1"/>
       <c r="M30" s="1"/>
       <c r="N30" s="1"/>
       <c r="O30" s="1"/>
-      <c r="P30" s="1"/>
+      <c r="P30" s="1" t="s">
+        <v>546</v>
+      </c>
     </row>
     <row r="31" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B31" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>580</v>
-      </c>
+        <v>547</v>
+      </c>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
-      <c r="I31" s="1"/>
+      <c r="I31" s="1" t="s">
+        <v>545</v>
+      </c>
       <c r="J31" s="1"/>
       <c r="K31" s="1"/>
-      <c r="L31" s="1" t="s">
-        <v>3</v>
-      </c>
+      <c r="L31" s="1"/>
       <c r="M31" s="1"/>
       <c r="N31" s="1"/>
       <c r="O31" s="1"/>
@@ -11527,9 +11899,11 @@
         <v>16</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>581</v>
-      </c>
-      <c r="E32" s="1"/>
+        <v>576</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>698</v>
+      </c>
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
@@ -11544,53 +11918,63 @@
       <c r="O32" s="1"/>
       <c r="P32" s="1"/>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B33" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C33" s="1"/>
-      <c r="D33" s="1"/>
-      <c r="E33" s="1"/>
+        <v>10</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>700</v>
+      </c>
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
       <c r="H33" s="1"/>
-      <c r="I33" s="1" t="s">
-        <v>109</v>
-      </c>
+      <c r="I33" s="1"/>
       <c r="J33" s="1"/>
       <c r="K33" s="1"/>
-      <c r="L33" s="1"/>
+      <c r="L33" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="M33" s="1"/>
       <c r="N33" s="1"/>
-      <c r="O33" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="O33" s="1"/>
       <c r="P33" s="1"/>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A34" s="8"/>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B34" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C34" s="1"/>
-      <c r="D34" s="1"/>
-      <c r="E34" s="1"/>
+        <v>10</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>701</v>
+      </c>
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
-      <c r="L34" s="1"/>
+      <c r="L34" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="M34" s="1"/>
       <c r="N34" s="1"/>
       <c r="O34" s="1"/>
       <c r="P34" s="1"/>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A35" s="8"/>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B35" s="1" t="s">
-        <v>108</v>
+        <v>2</v>
       </c>
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
@@ -11598,20 +11982,22 @@
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
-      <c r="I35" s="1"/>
+      <c r="I35" s="1" t="s">
+        <v>109</v>
+      </c>
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
       <c r="M35" s="1"/>
-      <c r="N35" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="O35" s="1"/>
+      <c r="N35" s="1"/>
+      <c r="O35" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="P35" s="1"/>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B36" s="1" t="s">
-        <v>547</v>
+        <v>59</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
@@ -11619,27 +12005,23 @@
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
-      <c r="I36" s="1" t="s">
-        <v>545</v>
-      </c>
+      <c r="I36" s="1"/>
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
       <c r="L36" s="1"/>
       <c r="M36" s="1"/>
       <c r="N36" s="1"/>
       <c r="O36" s="1"/>
-      <c r="P36" s="1"/>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="P36" s="1" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B37" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>582</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>583</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
       <c r="E37" s="1"/>
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
@@ -11647,75 +12029,75 @@
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
       <c r="K37" s="1"/>
-      <c r="L37" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="M37" s="1"/>
-      <c r="N37" s="1"/>
+      <c r="L37" s="1"/>
+      <c r="M37" s="1" t="s">
+        <v>774</v>
+      </c>
+      <c r="N37" s="1" t="s">
+        <v>106</v>
+      </c>
       <c r="O37" s="1"/>
       <c r="P37" s="1"/>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B38" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>582</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>584</v>
-      </c>
+        <v>608</v>
+      </c>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
       <c r="E38" s="1"/>
       <c r="F38" s="1"/>
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
-      <c r="I38" s="1"/>
+      <c r="I38" s="1" t="s">
+        <v>676</v>
+      </c>
       <c r="J38" s="1"/>
       <c r="K38" s="1"/>
-      <c r="L38" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="M38" s="1"/>
-      <c r="N38" s="1"/>
+      <c r="L38" s="1"/>
+      <c r="M38" s="1" t="s">
+        <v>675</v>
+      </c>
+      <c r="N38" s="1" t="s">
+        <v>106</v>
+      </c>
       <c r="O38" s="1"/>
       <c r="P38" s="1"/>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B39" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>586</v>
-      </c>
+        <v>547</v>
+      </c>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
       <c r="E39" s="1"/>
       <c r="F39" s="1"/>
       <c r="G39" s="1"/>
       <c r="H39" s="1"/>
-      <c r="I39" s="1"/>
+      <c r="I39" s="1" t="s">
+        <v>545</v>
+      </c>
       <c r="J39" s="1"/>
       <c r="K39" s="1"/>
-      <c r="L39" s="1" t="s">
-        <v>115</v>
-      </c>
+      <c r="L39" s="1"/>
       <c r="M39" s="1"/>
       <c r="N39" s="1"/>
       <c r="O39" s="1"/>
       <c r="P39" s="1"/>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B40" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>587</v>
-      </c>
-      <c r="E40" s="1"/>
+        <v>580</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>702</v>
+      </c>
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
       <c r="H40" s="1"/>
@@ -11730,67 +12112,67 @@
       <c r="O40" s="1"/>
       <c r="P40" s="1"/>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B41" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>582</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>588</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="C41" s="1"/>
+      <c r="D41" s="1"/>
       <c r="E41" s="1"/>
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
       <c r="H41" s="1"/>
-      <c r="I41" s="1"/>
+      <c r="I41" s="1" t="s">
+        <v>600</v>
+      </c>
       <c r="J41" s="1"/>
       <c r="K41" s="1"/>
-      <c r="L41" s="1" t="s">
-        <v>115</v>
-      </c>
+      <c r="L41" s="1"/>
       <c r="M41" s="1"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
       <c r="P41" s="1"/>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B42" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>589</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="C42" s="1"/>
+      <c r="D42" s="1"/>
       <c r="E42" s="1"/>
       <c r="F42" s="1"/>
-      <c r="G42" s="1"/>
+      <c r="G42" s="1" t="s">
+        <v>609</v>
+      </c>
       <c r="H42" s="1"/>
-      <c r="I42" s="1"/>
-      <c r="J42" s="1"/>
+      <c r="I42" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J42" s="1" t="s">
+        <v>56</v>
+      </c>
       <c r="K42" s="1"/>
-      <c r="L42" s="1" t="s">
-        <v>115</v>
-      </c>
+      <c r="L42" s="1"/>
       <c r="M42" s="1"/>
       <c r="N42" s="1"/>
       <c r="O42" s="1"/>
-      <c r="P42" s="1"/>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="P42" s="1" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B43" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>590</v>
-      </c>
-      <c r="E43" s="1"/>
+        <v>581</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>703</v>
+      </c>
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
       <c r="H43" s="1"/>
@@ -11805,7 +12187,7 @@
       <c r="O43" s="1"/>
       <c r="P43" s="1"/>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B44" s="1" t="s">
         <v>10</v>
       </c>
@@ -11813,9 +12195,11 @@
         <v>582</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>591</v>
-      </c>
-      <c r="E44" s="1"/>
+        <v>583</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>704</v>
+      </c>
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
       <c r="H44" s="1"/>
@@ -11830,17 +12214,19 @@
       <c r="O44" s="1"/>
       <c r="P44" s="1"/>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B45" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>585</v>
+        <v>579</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>592</v>
-      </c>
-      <c r="E45" s="1"/>
+        <v>584</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>705</v>
+      </c>
       <c r="F45" s="1"/>
       <c r="G45" s="1"/>
       <c r="H45" s="1"/>
@@ -11855,17 +12241,19 @@
       <c r="O45" s="1"/>
       <c r="P45" s="1"/>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B46" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>593</v>
-      </c>
-      <c r="E46" s="1"/>
+        <v>585</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>706</v>
+      </c>
       <c r="F46" s="1"/>
       <c r="G46" s="1"/>
       <c r="H46" s="1"/>
@@ -11880,7 +12268,7 @@
       <c r="O46" s="1"/>
       <c r="P46" s="1"/>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B47" s="1" t="s">
         <v>10</v>
       </c>
@@ -11888,9 +12276,11 @@
         <v>582</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>594</v>
-      </c>
-      <c r="E47" s="1"/>
+        <v>586</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>707</v>
+      </c>
       <c r="F47" s="1"/>
       <c r="G47" s="1"/>
       <c r="H47" s="1"/>
@@ -11905,22 +12295,28 @@
       <c r="O47" s="1"/>
       <c r="P47" s="1"/>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B48" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="1"/>
-      <c r="D48" s="1"/>
-      <c r="E48" s="1"/>
+        <v>10</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>708</v>
+      </c>
       <c r="F48" s="1"/>
       <c r="G48" s="1"/>
       <c r="H48" s="1"/>
-      <c r="I48" s="1" t="s">
-        <v>154</v>
-      </c>
+      <c r="I48" s="1"/>
       <c r="J48" s="1"/>
       <c r="K48" s="1"/>
-      <c r="L48" s="1"/>
+      <c r="L48" s="1" t="s">
+        <v>115</v>
+      </c>
       <c r="M48" s="1"/>
       <c r="N48" s="1"/>
       <c r="O48" s="1"/>
@@ -11928,45 +12324,53 @@
     </row>
     <row r="49" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B49" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C49" s="1"/>
-      <c r="D49" s="1"/>
-      <c r="E49" s="1"/>
+        <v>10</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>709</v>
+      </c>
       <c r="F49" s="1"/>
       <c r="G49" s="1"/>
       <c r="H49" s="1"/>
-      <c r="I49" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="J49" s="1" t="s">
-        <v>56</v>
-      </c>
+      <c r="I49" s="1"/>
+      <c r="J49" s="1"/>
       <c r="K49" s="1"/>
-      <c r="L49" s="1"/>
+      <c r="L49" s="1" t="s">
+        <v>115</v>
+      </c>
       <c r="M49" s="1"/>
       <c r="N49" s="1"/>
       <c r="O49" s="1"/>
-      <c r="P49" s="1" t="s">
-        <v>546</v>
-      </c>
+      <c r="P49" s="1"/>
     </row>
     <row r="50" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B50" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="C50" s="1"/>
-      <c r="D50" s="1"/>
-      <c r="E50" s="1"/>
+        <v>10</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>710</v>
+      </c>
       <c r="F50" s="1"/>
       <c r="G50" s="1"/>
       <c r="H50" s="1"/>
-      <c r="I50" s="1" t="s">
-        <v>545</v>
-      </c>
+      <c r="I50" s="1"/>
       <c r="J50" s="1"/>
       <c r="K50" s="1"/>
-      <c r="L50" s="1"/>
+      <c r="L50" s="1" t="s">
+        <v>115</v>
+      </c>
       <c r="M50" s="1"/>
       <c r="N50" s="1"/>
       <c r="O50" s="1"/>
@@ -11977,26 +12381,22 @@
         <v>10</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>16</v>
+        <v>579</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>595</v>
-      </c>
-      <c r="E51" s="1"/>
-      <c r="F51" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="G51" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H51" t="s">
-        <v>519</v>
-      </c>
+        <v>590</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="F51" s="1"/>
+      <c r="G51" s="1"/>
+      <c r="H51" s="1"/>
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
       <c r="K51" s="1"/>
       <c r="L51" s="1" t="s">
-        <v>3</v>
+        <v>115</v>
       </c>
       <c r="M51" s="1"/>
       <c r="N51" s="1"/>
@@ -12008,15 +12408,15 @@
         <v>10</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>596</v>
+        <v>579</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>597</v>
-      </c>
-      <c r="E52" s="1"/>
-      <c r="F52" s="1" t="s">
-        <v>52</v>
-      </c>
+        <v>591</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="F52" s="1"/>
       <c r="G52" s="1"/>
       <c r="H52" s="1"/>
       <c r="I52" s="1"/>
@@ -12032,24 +12432,20 @@
     </row>
     <row r="53" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B53" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>596</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>598</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="C53" s="1"/>
+      <c r="D53" s="1"/>
       <c r="E53" s="1"/>
       <c r="F53" s="1"/>
       <c r="G53" s="1"/>
       <c r="H53" s="1"/>
-      <c r="I53" s="1"/>
+      <c r="I53" s="1" t="s">
+        <v>154</v>
+      </c>
       <c r="J53" s="1"/>
       <c r="K53" s="1"/>
-      <c r="L53" s="1" t="s">
-        <v>115</v>
-      </c>
+      <c r="L53" s="1"/>
       <c r="M53" s="1"/>
       <c r="N53" s="1"/>
       <c r="O53" s="1"/>
@@ -12057,57 +12453,39 @@
     </row>
     <row r="54" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B54" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>599</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="C54" s="1"/>
+      <c r="D54" s="1"/>
       <c r="E54" s="1"/>
-      <c r="F54" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="G54" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H54" t="s">
-        <v>600</v>
-      </c>
-      <c r="I54" s="1"/>
-      <c r="J54" s="1"/>
+      <c r="F54" s="1"/>
+      <c r="G54" s="1"/>
+      <c r="H54" s="1"/>
       <c r="K54" s="1"/>
-      <c r="L54" s="1" t="s">
-        <v>3</v>
-      </c>
+      <c r="L54" s="1"/>
       <c r="M54" s="1"/>
       <c r="N54" s="1"/>
       <c r="O54" s="1"/>
-      <c r="P54" s="1"/>
+      <c r="P54" s="1" t="s">
+        <v>672</v>
+      </c>
     </row>
     <row r="55" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B55" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>582</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>601</v>
-      </c>
+        <v>547</v>
+      </c>
+      <c r="C55" s="1"/>
+      <c r="D55" s="1"/>
       <c r="E55" s="1"/>
-      <c r="F55" s="1" t="s">
-        <v>52</v>
-      </c>
+      <c r="F55" s="1"/>
       <c r="G55" s="1"/>
       <c r="H55" s="1"/>
-      <c r="I55" s="1"/>
+      <c r="I55" s="1" t="s">
+        <v>545</v>
+      </c>
       <c r="J55" s="1"/>
       <c r="K55" s="1"/>
-      <c r="L55" s="1" t="s">
-        <v>115</v>
-      </c>
+      <c r="L55" s="1"/>
       <c r="M55" s="1"/>
       <c r="N55" s="1"/>
       <c r="O55" s="1"/>
@@ -12118,20 +12496,28 @@
         <v>10</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>582</v>
+        <v>16</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>602</v>
-      </c>
-      <c r="E56" s="1"/>
-      <c r="F56" s="1"/>
-      <c r="G56" s="1"/>
-      <c r="H56" s="1"/>
+        <v>776</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H56" t="s">
+        <v>519</v>
+      </c>
       <c r="I56" s="1"/>
       <c r="J56" s="1"/>
       <c r="K56" s="1"/>
       <c r="L56" s="1" t="s">
-        <v>115</v>
+        <v>3</v>
       </c>
       <c r="M56" s="1"/>
       <c r="N56" s="1"/>
@@ -12143,26 +12529,24 @@
         <v>10</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>16</v>
+        <v>777</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>603</v>
-      </c>
-      <c r="E57" s="1"/>
+        <v>593</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>693</v>
+      </c>
       <c r="F57" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="G57" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H57" t="s">
-        <v>548</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G57" s="1"/>
+      <c r="H57" s="1"/>
       <c r="I57" s="1"/>
       <c r="J57" s="1"/>
       <c r="K57" s="1"/>
       <c r="L57" s="1" t="s">
-        <v>3</v>
+        <v>115</v>
       </c>
       <c r="M57" s="1"/>
       <c r="N57" s="1"/>
@@ -12171,20 +12555,26 @@
     </row>
     <row r="58" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B58" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="1"/>
-      <c r="D58" s="1"/>
-      <c r="E58" s="1"/>
+        <v>10</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>777</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>714</v>
+      </c>
       <c r="F58" s="1"/>
       <c r="G58" s="1"/>
       <c r="H58" s="1"/>
-      <c r="I58" s="9" t="s">
-        <v>604</v>
-      </c>
+      <c r="I58" s="1"/>
       <c r="J58" s="1"/>
       <c r="K58" s="1"/>
-      <c r="L58" s="1"/>
+      <c r="L58" s="1" t="s">
+        <v>115</v>
+      </c>
       <c r="M58" s="1"/>
       <c r="N58" s="1"/>
       <c r="O58" s="1"/>
@@ -12192,43 +12582,61 @@
     </row>
     <row r="59" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B59" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C59" s="1"/>
-      <c r="D59" s="1"/>
-      <c r="E59" s="1"/>
-      <c r="F59" s="1"/>
-      <c r="G59" s="1"/>
-      <c r="H59" s="1"/>
-      <c r="I59" s="1" t="s">
-        <v>605</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>715</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H59" t="s">
+        <v>596</v>
+      </c>
+      <c r="I59" s="1"/>
       <c r="J59" s="1"/>
       <c r="K59" s="1"/>
-      <c r="L59" s="1"/>
+      <c r="L59" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="M59" s="1"/>
       <c r="N59" s="1"/>
       <c r="O59" s="1"/>
-      <c r="P59" s="1" t="s">
-        <v>310</v>
-      </c>
+      <c r="P59" s="1"/>
     </row>
     <row r="60" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B60" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="C60" s="1"/>
-      <c r="D60" s="1"/>
-      <c r="E60" s="1"/>
-      <c r="F60" s="1"/>
+        <v>10</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>716</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>52</v>
+      </c>
       <c r="G60" s="1"/>
       <c r="H60" s="1"/>
-      <c r="I60" s="1" t="s">
-        <v>545</v>
-      </c>
+      <c r="I60" s="1"/>
       <c r="J60" s="1"/>
       <c r="K60" s="1"/>
-      <c r="L60" s="1"/>
+      <c r="L60" s="1" t="s">
+        <v>115</v>
+      </c>
       <c r="M60" s="1"/>
       <c r="N60" s="1"/>
       <c r="O60" s="1"/>
@@ -12239,13 +12647,13 @@
         <v>10</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>91</v>
+        <v>579</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>357</v>
+        <v>598</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>358</v>
+        <v>717</v>
       </c>
       <c r="F61" s="1"/>
       <c r="G61" s="1"/>
@@ -12254,7 +12662,7 @@
       <c r="J61" s="1"/>
       <c r="K61" s="1"/>
       <c r="L61" s="1" t="s">
-        <v>88</v>
+        <v>115</v>
       </c>
       <c r="M61" s="1"/>
       <c r="N61" s="1"/>
@@ -12266,22 +12674,28 @@
         <v>10</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>91</v>
+        <v>16</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>359</v>
+        <v>599</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="F62" s="1"/>
-      <c r="G62" s="1"/>
-      <c r="H62" s="1"/>
+        <v>699</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H62" t="s">
+        <v>548</v>
+      </c>
       <c r="I62" s="1"/>
       <c r="J62" s="1"/>
       <c r="K62" s="1"/>
       <c r="L62" s="1" t="s">
-        <v>88</v>
+        <v>3</v>
       </c>
       <c r="M62" s="1"/>
       <c r="N62" s="1"/>
@@ -12298,8 +12712,8 @@
       <c r="F63" s="1"/>
       <c r="G63" s="1"/>
       <c r="H63" s="1"/>
-      <c r="I63" s="9" t="s">
-        <v>604</v>
+      <c r="I63" s="1" t="s">
+        <v>600</v>
       </c>
       <c r="J63" s="1"/>
       <c r="K63" s="1"/>
@@ -12311,7 +12725,7 @@
     </row>
     <row r="64" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B64" s="1" t="s">
-        <v>59</v>
+        <v>677</v>
       </c>
       <c r="C64" s="1"/>
       <c r="D64" s="1"/>
@@ -12319,9 +12733,7 @@
       <c r="F64" s="1"/>
       <c r="G64" s="1"/>
       <c r="H64" s="1"/>
-      <c r="I64" s="1" t="s">
-        <v>285</v>
-      </c>
+      <c r="I64" s="1"/>
       <c r="J64" s="1"/>
       <c r="K64" s="1"/>
       <c r="L64" s="1"/>
@@ -12329,12 +12741,12 @@
       <c r="N64" s="1"/>
       <c r="O64" s="1"/>
       <c r="P64" s="1" t="s">
-        <v>493</v>
+        <v>52</v>
       </c>
     </row>
     <row r="65" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B65" s="1" t="s">
-        <v>547</v>
+        <v>59</v>
       </c>
       <c r="C65" s="1"/>
       <c r="D65" s="1"/>
@@ -12343,7 +12755,7 @@
       <c r="G65" s="1"/>
       <c r="H65" s="1"/>
       <c r="I65" s="1" t="s">
-        <v>545</v>
+        <v>601</v>
       </c>
       <c r="J65" s="1"/>
       <c r="K65" s="1"/>
@@ -12351,30 +12763,28 @@
       <c r="M65" s="1"/>
       <c r="N65" s="1"/>
       <c r="O65" s="1"/>
-      <c r="P65" s="1"/>
+      <c r="P65" s="1" t="s">
+        <v>310</v>
+      </c>
     </row>
     <row r="66" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B66" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>507</v>
-      </c>
-      <c r="E66" s="1" t="s">
-        <v>508</v>
-      </c>
+        <v>547</v>
+      </c>
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
+      <c r="E66" s="1"/>
       <c r="F66" s="1"/>
       <c r="G66" s="1"/>
       <c r="H66" s="1"/>
-      <c r="I66" s="1"/>
+      <c r="I66" s="1" t="s">
+        <v>545</v>
+      </c>
       <c r="J66" s="1"/>
-      <c r="K66" s="1"/>
-      <c r="L66" s="1" t="s">
-        <v>3</v>
-      </c>
+      <c r="K66" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="L66" s="1"/>
       <c r="M66" s="1"/>
       <c r="N66" s="1"/>
       <c r="O66" s="1"/>
@@ -12385,13 +12795,13 @@
         <v>10</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>9</v>
+        <v>91</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>509</v>
+        <v>357</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>510</v>
+        <v>358</v>
       </c>
       <c r="F67" s="1"/>
       <c r="G67" s="1"/>
@@ -12400,7 +12810,7 @@
       <c r="J67" s="1"/>
       <c r="K67" s="1"/>
       <c r="L67" s="1" t="s">
-        <v>3</v>
+        <v>88</v>
       </c>
       <c r="M67" s="1"/>
       <c r="N67" s="1"/>
@@ -12412,13 +12822,13 @@
         <v>10</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>9</v>
+        <v>91</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>511</v>
+        <v>359</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>512</v>
+        <v>360</v>
       </c>
       <c r="F68" s="1"/>
       <c r="G68" s="1"/>
@@ -12427,7 +12837,7 @@
       <c r="J68" s="1"/>
       <c r="K68" s="1"/>
       <c r="L68" s="1" t="s">
-        <v>3</v>
+        <v>88</v>
       </c>
       <c r="M68" s="1"/>
       <c r="N68" s="1"/>
@@ -12444,8 +12854,8 @@
       <c r="F69" s="1"/>
       <c r="G69" s="1"/>
       <c r="H69" s="1"/>
-      <c r="I69" s="9" t="s">
-        <v>604</v>
+      <c r="I69" s="1" t="s">
+        <v>600</v>
       </c>
       <c r="J69" s="1"/>
       <c r="K69" s="1"/>
@@ -12475,7 +12885,7 @@
       <c r="N70" s="1"/>
       <c r="O70" s="1"/>
       <c r="P70" s="1" t="s">
-        <v>385</v>
+        <v>493</v>
       </c>
     </row>
     <row r="71" spans="2:16" x14ac:dyDescent="0.3">
@@ -12492,7 +12902,9 @@
         <v>545</v>
       </c>
       <c r="J71" s="1"/>
-      <c r="K71" s="1"/>
+      <c r="K71" s="1" t="s">
+        <v>553</v>
+      </c>
       <c r="L71" s="1"/>
       <c r="M71" s="1"/>
       <c r="N71" s="1"/>
@@ -12504,13 +12916,13 @@
         <v>10</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>440</v>
+        <v>507</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>441</v>
+        <v>508</v>
       </c>
       <c r="F72" s="1"/>
       <c r="G72" s="1"/>
@@ -12531,13 +12943,13 @@
         <v>10</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>442</v>
+        <v>509</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>443</v>
+        <v>510</v>
       </c>
       <c r="F73" s="1"/>
       <c r="G73" s="1"/>
@@ -12555,18 +12967,26 @@
     </row>
     <row r="74" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B74" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C74" s="1"/>
-      <c r="D74" s="1"/>
-      <c r="E74" s="1"/>
+        <v>10</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>512</v>
+      </c>
       <c r="F74" s="1"/>
       <c r="G74" s="1"/>
       <c r="H74" s="1"/>
       <c r="I74" s="1"/>
       <c r="J74" s="1"/>
       <c r="K74" s="1"/>
-      <c r="L74" s="1"/>
+      <c r="L74" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="M74" s="1"/>
       <c r="N74" s="1"/>
       <c r="O74" s="1"/>
@@ -12574,7 +12994,7 @@
     </row>
     <row r="75" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B75" s="1" t="s">
-        <v>108</v>
+        <v>2</v>
       </c>
       <c r="C75" s="1"/>
       <c r="D75" s="1"/>
@@ -12582,20 +13002,20 @@
       <c r="F75" s="1"/>
       <c r="G75" s="1"/>
       <c r="H75" s="1"/>
-      <c r="I75" s="1"/>
+      <c r="I75" s="1" t="s">
+        <v>600</v>
+      </c>
       <c r="J75" s="1"/>
       <c r="K75" s="1"/>
       <c r="L75" s="1"/>
       <c r="M75" s="1"/>
-      <c r="N75" s="1" t="s">
-        <v>265</v>
-      </c>
+      <c r="N75" s="1"/>
       <c r="O75" s="1"/>
       <c r="P75" s="1"/>
     </row>
     <row r="76" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B76" s="1" t="s">
-        <v>547</v>
+        <v>59</v>
       </c>
       <c r="C76" s="1"/>
       <c r="D76" s="1"/>
@@ -12604,7 +13024,7 @@
       <c r="G76" s="1"/>
       <c r="H76" s="1"/>
       <c r="I76" s="1" t="s">
-        <v>545</v>
+        <v>285</v>
       </c>
       <c r="J76" s="1"/>
       <c r="K76" s="1"/>
@@ -12612,28 +13032,28 @@
       <c r="M76" s="1"/>
       <c r="N76" s="1"/>
       <c r="O76" s="1"/>
-      <c r="P76" s="1"/>
+      <c r="P76" s="1" t="s">
+        <v>385</v>
+      </c>
     </row>
     <row r="77" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B77" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>606</v>
-      </c>
+        <v>547</v>
+      </c>
+      <c r="C77" s="1"/>
+      <c r="D77" s="1"/>
       <c r="E77" s="1"/>
       <c r="F77" s="1"/>
       <c r="G77" s="1"/>
       <c r="H77" s="1"/>
-      <c r="I77" s="1"/>
+      <c r="I77" s="1" t="s">
+        <v>545</v>
+      </c>
       <c r="J77" s="1"/>
-      <c r="K77" s="1"/>
-      <c r="L77" s="1" t="s">
-        <v>3</v>
-      </c>
+      <c r="K77" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="L77" s="1"/>
       <c r="M77" s="1"/>
       <c r="N77" s="1"/>
       <c r="O77" s="1"/>
@@ -12644,21 +13064,17 @@
         <v>10</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>607</v>
-      </c>
-      <c r="E78" s="1"/>
-      <c r="F78" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="G78" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H78" t="s">
-        <v>573</v>
-      </c>
+        <v>440</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
       <c r="I78" s="1"/>
       <c r="J78" s="1"/>
       <c r="K78" s="1"/>
@@ -12678,18 +13094,14 @@
         <v>24</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="E79" s="1"/>
-      <c r="F79" s="1" t="s">
-        <v>560</v>
-      </c>
-      <c r="G79" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H79" s="1" t="s">
-        <v>608</v>
-      </c>
+        <v>442</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="F79" s="1"/>
+      <c r="G79" s="1"/>
+      <c r="H79" s="1"/>
       <c r="I79" s="1"/>
       <c r="J79" s="1"/>
       <c r="K79" s="1"/>
@@ -12703,7 +13115,7 @@
     </row>
     <row r="80" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B80" s="1" t="s">
-        <v>547</v>
+        <v>2</v>
       </c>
       <c r="C80" s="1"/>
       <c r="D80" s="1"/>
@@ -12711,7 +13123,9 @@
       <c r="F80" s="1"/>
       <c r="G80" s="1"/>
       <c r="H80" s="1"/>
-      <c r="I80" s="1"/>
+      <c r="I80" s="1" t="s">
+        <v>600</v>
+      </c>
       <c r="J80" s="1"/>
       <c r="K80" s="1"/>
       <c r="L80" s="1"/>
@@ -12722,33 +13136,29 @@
     </row>
     <row r="81" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B81" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C81" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D81" s="1" t="s">
-        <v>609</v>
-      </c>
+        <v>674</v>
+      </c>
+      <c r="C81" s="1"/>
+      <c r="D81" s="1"/>
       <c r="E81" s="1"/>
-      <c r="F81" s="1" t="s">
-        <v>52</v>
-      </c>
+      <c r="F81" s="1"/>
       <c r="G81" s="1"/>
+      <c r="H81" s="1"/>
       <c r="I81" s="1"/>
       <c r="J81" s="1"/>
       <c r="K81" s="1"/>
-      <c r="L81" s="1" t="s">
-        <v>3</v>
-      </c>
+      <c r="L81" s="1"/>
       <c r="M81" s="1"/>
       <c r="N81" s="1"/>
       <c r="O81" s="1"/>
-      <c r="P81" s="1"/>
+      <c r="P81" s="1" t="s">
+        <v>673</v>
+      </c>
     </row>
     <row r="82" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A82" s="9"/>
       <c r="B82" s="1" t="s">
-        <v>547</v>
+        <v>108</v>
       </c>
       <c r="C82" s="1"/>
       <c r="D82" s="1"/>
@@ -12758,41 +13168,33 @@
       <c r="H82" s="1"/>
       <c r="I82" s="1"/>
       <c r="J82" s="1"/>
-      <c r="K82" s="1" t="s">
-        <v>554</v>
-      </c>
+      <c r="K82" s="1"/>
       <c r="L82" s="1"/>
-      <c r="M82" s="1"/>
-      <c r="N82" s="1"/>
+      <c r="M82" s="1" t="s">
+        <v>775</v>
+      </c>
+      <c r="N82" s="1" t="s">
+        <v>106</v>
+      </c>
       <c r="O82" s="1"/>
       <c r="P82" s="1"/>
     </row>
     <row r="83" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B83" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D83" s="1" t="s">
-        <v>610</v>
-      </c>
+        <v>547</v>
+      </c>
+      <c r="C83" s="1"/>
+      <c r="D83" s="1"/>
       <c r="E83" s="1"/>
-      <c r="F83" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="G83" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H83" t="s">
-        <v>611</v>
-      </c>
-      <c r="I83" s="1"/>
+      <c r="F83" s="1"/>
+      <c r="G83" s="1"/>
+      <c r="H83" s="1"/>
+      <c r="I83" s="1" t="s">
+        <v>545</v>
+      </c>
       <c r="J83" s="1"/>
       <c r="K83" s="1"/>
-      <c r="L83" s="1" t="s">
-        <v>3</v>
-      </c>
+      <c r="L83" s="1"/>
       <c r="M83" s="1"/>
       <c r="N83" s="1"/>
       <c r="O83" s="1"/>
@@ -12800,26 +13202,32 @@
     </row>
     <row r="84" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B84" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="C84" s="1"/>
-      <c r="D84" s="1"/>
-      <c r="E84" s="1"/>
+        <v>10</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>718</v>
+      </c>
       <c r="F84" s="1"/>
       <c r="G84" s="1"/>
       <c r="H84" s="1"/>
       <c r="I84" s="1"/>
       <c r="J84" s="1"/>
-      <c r="K84" s="1" t="s">
-        <v>554</v>
-      </c>
-      <c r="L84" s="1"/>
+      <c r="K84" s="1"/>
+      <c r="L84" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="M84" s="1"/>
       <c r="N84" s="1"/>
       <c r="O84" s="1"/>
       <c r="P84" s="1"/>
     </row>
-    <row r="85" spans="1:16" ht="24" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B85" s="1" t="s">
         <v>10</v>
       </c>
@@ -12827,17 +13235,19 @@
         <v>16</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>612</v>
-      </c>
-      <c r="E85" s="10"/>
+        <v>603</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>719</v>
+      </c>
       <c r="F85" s="1" t="s">
         <v>294</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H85" t="s">
-        <v>613</v>
+        <v>571</v>
       </c>
       <c r="I85" s="1"/>
       <c r="J85" s="1"/>
@@ -12852,29 +13262,38 @@
     </row>
     <row r="86" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B86" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="C86" s="1"/>
-      <c r="D86" s="1"/>
+        <v>10</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>534</v>
+      </c>
       <c r="E86" s="1"/>
-      <c r="F86" s="1"/>
-      <c r="G86" s="1"/>
-      <c r="H86" s="1"/>
+      <c r="F86" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="G86" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H86" s="1" t="s">
+        <v>604</v>
+      </c>
       <c r="I86" s="1"/>
       <c r="J86" s="1"/>
-      <c r="K86" s="1" t="s">
-        <v>554</v>
-      </c>
-      <c r="L86" s="1"/>
+      <c r="K86" s="1"/>
+      <c r="L86" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="M86" s="1"/>
       <c r="N86" s="1"/>
       <c r="O86" s="1"/>
       <c r="P86" s="1"/>
     </row>
     <row r="87" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A87" s="8"/>
       <c r="B87" s="1" t="s">
-        <v>614</v>
+        <v>547</v>
       </c>
       <c r="C87" s="1"/>
       <c r="D87" s="1"/>
@@ -12887,28 +13306,33 @@
       <c r="K87" s="1"/>
       <c r="L87" s="1"/>
       <c r="M87" s="1"/>
-      <c r="N87" s="1" t="s">
-        <v>615</v>
-      </c>
+      <c r="N87" s="1"/>
       <c r="O87" s="1"/>
       <c r="P87" s="1"/>
     </row>
     <row r="88" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B88" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C88" s="1"/>
-      <c r="D88" s="1"/>
-      <c r="E88" s="1"/>
-      <c r="F88" s="1"/>
+        <v>10</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>52</v>
+      </c>
       <c r="G88" s="1"/>
-      <c r="H88" s="1"/>
-      <c r="I88" s="1" t="s">
-        <v>154</v>
-      </c>
+      <c r="I88" s="1"/>
       <c r="J88" s="1"/>
       <c r="K88" s="1"/>
-      <c r="L88" s="1"/>
+      <c r="L88" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="M88" s="1"/>
       <c r="N88" s="1"/>
       <c r="O88" s="1"/>
@@ -12916,7 +13340,7 @@
     </row>
     <row r="89" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B89" s="1" t="s">
-        <v>59</v>
+        <v>547</v>
       </c>
       <c r="C89" s="1"/>
       <c r="D89" s="1"/>
@@ -12926,31 +13350,40 @@
       <c r="H89" s="1"/>
       <c r="I89" s="1"/>
       <c r="J89" s="1"/>
-      <c r="K89" s="1"/>
+      <c r="K89" s="1" t="s">
+        <v>553</v>
+      </c>
       <c r="L89" s="1"/>
       <c r="M89" s="1"/>
       <c r="N89" s="1"/>
       <c r="O89" s="1"/>
-      <c r="P89" s="1" t="s">
-        <v>546</v>
-      </c>
+      <c r="P89" s="1"/>
     </row>
     <row r="90" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B90" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="C90" s="1"/>
-      <c r="D90" s="1"/>
-      <c r="E90" s="1"/>
-      <c r="F90" s="1"/>
-      <c r="G90" s="1"/>
-      <c r="H90" s="1"/>
-      <c r="I90" s="1" t="s">
-        <v>545</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>720</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="G90" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I90" s="1"/>
       <c r="J90" s="1"/>
       <c r="K90" s="1"/>
-      <c r="L90" s="1"/>
+      <c r="L90" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="M90" s="1"/>
       <c r="N90" s="1"/>
       <c r="O90" s="1"/>
@@ -12958,24 +13391,20 @@
     </row>
     <row r="91" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B91" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C91" s="1" t="s">
-        <v>582</v>
-      </c>
-      <c r="D91" s="1" t="s">
-        <v>616</v>
-      </c>
+        <v>547</v>
+      </c>
+      <c r="C91" s="1"/>
+      <c r="D91" s="1"/>
       <c r="E91" s="1"/>
       <c r="F91" s="1"/>
       <c r="G91" s="1"/>
       <c r="H91" s="1"/>
       <c r="I91" s="1"/>
       <c r="J91" s="1"/>
-      <c r="K91" s="1"/>
-      <c r="L91" s="1" t="s">
-        <v>115</v>
-      </c>
+      <c r="K91" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="L91" s="1"/>
       <c r="M91" s="1"/>
       <c r="N91" s="1"/>
       <c r="O91" s="1"/>
@@ -12986,20 +13415,25 @@
         <v>10</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>582</v>
+        <v>16</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>617</v>
-      </c>
-      <c r="E92" s="1"/>
-      <c r="F92" s="1"/>
-      <c r="G92" s="1"/>
-      <c r="H92" s="1"/>
+        <v>607</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>721</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="G92" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="I92" s="1"/>
       <c r="J92" s="1"/>
       <c r="K92" s="1"/>
       <c r="L92" s="1" t="s">
-        <v>115</v>
+        <v>3</v>
       </c>
       <c r="M92" s="1"/>
       <c r="N92" s="1"/>
@@ -13008,39 +13442,32 @@
     </row>
     <row r="93" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B93" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C93" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>618</v>
-      </c>
+        <v>547</v>
+      </c>
+      <c r="C93" s="1"/>
+      <c r="D93" s="1"/>
       <c r="E93" s="1"/>
       <c r="F93" s="1"/>
       <c r="G93" s="1"/>
       <c r="H93" s="1"/>
       <c r="I93" s="1"/>
       <c r="J93" s="1"/>
-      <c r="K93" s="1"/>
-      <c r="L93" s="1" t="s">
-        <v>115</v>
-      </c>
+      <c r="K93" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="L93" s="1"/>
       <c r="M93" s="1"/>
       <c r="N93" s="1"/>
       <c r="O93" s="1"/>
       <c r="P93" s="1"/>
     </row>
     <row r="94" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A94" s="9"/>
       <c r="B94" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C94" s="1" t="s">
-        <v>582</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>619</v>
-      </c>
+        <v>608</v>
+      </c>
+      <c r="C94" s="1"/>
+      <c r="D94" s="1"/>
       <c r="E94" s="1"/>
       <c r="F94" s="1"/>
       <c r="G94" s="1"/>
@@ -13048,34 +13475,32 @@
       <c r="I94" s="1"/>
       <c r="J94" s="1"/>
       <c r="K94" s="1"/>
-      <c r="L94" s="1" t="s">
-        <v>115</v>
-      </c>
+      <c r="L94" s="1"/>
       <c r="M94" s="1"/>
-      <c r="N94" s="1"/>
+      <c r="N94" s="1" t="s">
+        <v>553</v>
+      </c>
       <c r="O94" s="1"/>
-      <c r="P94" s="1"/>
+      <c r="P94" s="1" t="s">
+        <v>678</v>
+      </c>
     </row>
     <row r="95" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B95" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C95" s="1" t="s">
-        <v>582</v>
-      </c>
-      <c r="D95" s="1" t="s">
-        <v>620</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="C95" s="1"/>
+      <c r="D95" s="1"/>
       <c r="E95" s="1"/>
       <c r="F95" s="1"/>
       <c r="G95" s="1"/>
       <c r="H95" s="1"/>
-      <c r="I95" s="1"/>
+      <c r="I95" s="1" t="s">
+        <v>154</v>
+      </c>
       <c r="J95" s="1"/>
       <c r="K95" s="1"/>
-      <c r="L95" s="1" t="s">
-        <v>115</v>
-      </c>
+      <c r="L95" s="1"/>
       <c r="M95" s="1"/>
       <c r="N95" s="1"/>
       <c r="O95" s="1"/>
@@ -13083,57 +13508,41 @@
     </row>
     <row r="96" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B96" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C96" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D96" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="E96" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="F96" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="G96" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H96" t="s">
-        <v>519</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="C96" s="1"/>
+      <c r="D96" s="1"/>
+      <c r="E96" s="1"/>
+      <c r="F96" s="1"/>
+      <c r="G96" s="1"/>
+      <c r="H96" s="1"/>
       <c r="I96" s="1"/>
       <c r="J96" s="1"/>
       <c r="K96" s="1"/>
-      <c r="L96" s="1" t="s">
-        <v>3</v>
-      </c>
+      <c r="L96" s="1"/>
       <c r="M96" s="1"/>
       <c r="N96" s="1"/>
       <c r="O96" s="1"/>
-      <c r="P96" s="1"/>
+      <c r="P96" s="1" t="s">
+        <v>672</v>
+      </c>
     </row>
     <row r="97" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B97" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C97" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D97" s="1" t="s">
-        <v>622</v>
-      </c>
+        <v>547</v>
+      </c>
+      <c r="C97" s="1"/>
+      <c r="D97" s="1"/>
       <c r="E97" s="1"/>
       <c r="F97" s="1"/>
       <c r="G97" s="1"/>
       <c r="H97" s="1"/>
-      <c r="I97" s="1"/>
+      <c r="I97" s="1" t="s">
+        <v>545</v>
+      </c>
       <c r="J97" s="1"/>
       <c r="K97" s="1"/>
-      <c r="L97" s="1" t="s">
-        <v>3</v>
-      </c>
+      <c r="L97" s="1"/>
       <c r="M97" s="1"/>
       <c r="N97" s="1"/>
       <c r="O97" s="1"/>
@@ -13144,12 +13553,14 @@
         <v>10</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>16</v>
+        <v>579</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>623</v>
-      </c>
-      <c r="E98" s="1"/>
+        <v>610</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>722</v>
+      </c>
       <c r="F98" s="1"/>
       <c r="G98" s="1"/>
       <c r="H98" s="1"/>
@@ -13157,7 +13568,7 @@
       <c r="J98" s="1"/>
       <c r="K98" s="1"/>
       <c r="L98" s="1" t="s">
-        <v>3</v>
+        <v>115</v>
       </c>
       <c r="M98" s="1"/>
       <c r="N98" s="1"/>
@@ -13169,12 +13580,14 @@
         <v>10</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>16</v>
+        <v>579</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>624</v>
-      </c>
-      <c r="E99" s="1"/>
+        <v>611</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>723</v>
+      </c>
       <c r="F99" s="1"/>
       <c r="G99" s="1"/>
       <c r="H99" s="1"/>
@@ -13182,7 +13595,7 @@
       <c r="J99" s="1"/>
       <c r="K99" s="1"/>
       <c r="L99" s="1" t="s">
-        <v>3</v>
+        <v>115</v>
       </c>
       <c r="M99" s="1"/>
       <c r="N99" s="1"/>
@@ -13194,22 +13607,22 @@
         <v>10</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>596</v>
+        <v>582</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>625</v>
-      </c>
-      <c r="E100" s="1"/>
-      <c r="F100" s="1" t="s">
-        <v>52</v>
-      </c>
+        <v>612</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="F100" s="1"/>
       <c r="G100" s="1"/>
       <c r="H100" s="1"/>
       <c r="I100" s="1"/>
       <c r="J100" s="1"/>
       <c r="K100" s="1"/>
       <c r="L100" s="1" t="s">
-        <v>633</v>
+        <v>115</v>
       </c>
       <c r="M100" s="1"/>
       <c r="N100" s="1"/>
@@ -13221,12 +13634,14 @@
         <v>10</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>626</v>
+        <v>579</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>628</v>
-      </c>
-      <c r="E101" s="1"/>
+        <v>613</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>725</v>
+      </c>
       <c r="F101" s="1"/>
       <c r="G101" s="1"/>
       <c r="H101" s="1"/>
@@ -13234,7 +13649,7 @@
       <c r="J101" s="1"/>
       <c r="K101" s="1"/>
       <c r="L101" s="1" t="s">
-        <v>633</v>
+        <v>115</v>
       </c>
       <c r="M101" s="1"/>
       <c r="N101" s="1"/>
@@ -13246,12 +13661,14 @@
         <v>10</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>627</v>
+        <v>579</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>629</v>
-      </c>
-      <c r="E102" s="1"/>
+        <v>614</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>726</v>
+      </c>
       <c r="F102" s="1"/>
       <c r="G102" s="1"/>
       <c r="H102" s="1"/>
@@ -13259,7 +13676,7 @@
       <c r="J102" s="1"/>
       <c r="K102" s="1"/>
       <c r="L102" s="1" t="s">
-        <v>633</v>
+        <v>115</v>
       </c>
       <c r="M102" s="1"/>
       <c r="N102" s="1"/>
@@ -13271,20 +13688,28 @@
         <v>10</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>582</v>
+        <v>16</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>630</v>
-      </c>
-      <c r="E103" s="1"/>
-      <c r="F103" s="1"/>
-      <c r="G103" s="1"/>
-      <c r="H103" s="1"/>
+        <v>386</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="G103" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H103" t="s">
+        <v>519</v>
+      </c>
       <c r="I103" s="1"/>
       <c r="J103" s="1"/>
       <c r="K103" s="1"/>
       <c r="L103" s="1" t="s">
-        <v>115</v>
+        <v>3</v>
       </c>
       <c r="M103" s="1"/>
       <c r="N103" s="1"/>
@@ -13296,12 +13721,14 @@
         <v>10</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>582</v>
+        <v>16</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>631</v>
-      </c>
-      <c r="E104" s="1"/>
+        <v>616</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>728</v>
+      </c>
       <c r="F104" s="1"/>
       <c r="G104" s="1"/>
       <c r="H104" s="1"/>
@@ -13309,7 +13736,7 @@
       <c r="J104" s="1"/>
       <c r="K104" s="1"/>
       <c r="L104" s="1" t="s">
-        <v>115</v>
+        <v>3</v>
       </c>
       <c r="M104" s="1"/>
       <c r="N104" s="1"/>
@@ -13321,12 +13748,14 @@
         <v>10</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>585</v>
+        <v>16</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>632</v>
-      </c>
-      <c r="E105" s="1"/>
+        <v>617</v>
+      </c>
+      <c r="E105" s="1" t="s">
+        <v>730</v>
+      </c>
       <c r="F105" s="1"/>
       <c r="G105" s="1"/>
       <c r="H105" s="1"/>
@@ -13334,7 +13763,7 @@
       <c r="J105" s="1"/>
       <c r="K105" s="1"/>
       <c r="L105" s="1" t="s">
-        <v>115</v>
+        <v>3</v>
       </c>
       <c r="M105" s="1"/>
       <c r="N105" s="1"/>
@@ -13349,13 +13778,14 @@
         <v>16</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>386</v>
+        <v>618</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>387</v>
+        <v>729</v>
       </c>
       <c r="F106" s="1"/>
       <c r="G106" s="1"/>
+      <c r="H106" s="1"/>
       <c r="I106" s="1"/>
       <c r="J106" s="1"/>
       <c r="K106" s="1"/>
@@ -13372,20 +13802,24 @@
         <v>10</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>582</v>
+        <v>592</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>634</v>
-      </c>
-      <c r="E107" s="1"/>
-      <c r="F107" s="1"/>
+        <v>619</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>731</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>52</v>
+      </c>
       <c r="G107" s="1"/>
       <c r="H107" s="1"/>
       <c r="I107" s="1"/>
       <c r="J107" s="1"/>
       <c r="K107" s="1"/>
       <c r="L107" s="1" t="s">
-        <v>115</v>
+        <v>627</v>
       </c>
       <c r="M107" s="1"/>
       <c r="N107" s="1"/>
@@ -13397,12 +13831,14 @@
         <v>10</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>582</v>
+        <v>620</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>635</v>
-      </c>
-      <c r="E108" s="1"/>
+        <v>622</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>732</v>
+      </c>
       <c r="F108" s="1"/>
       <c r="G108" s="1"/>
       <c r="H108" s="1"/>
@@ -13410,7 +13846,7 @@
       <c r="J108" s="1"/>
       <c r="K108" s="1"/>
       <c r="L108" s="1" t="s">
-        <v>115</v>
+        <v>627</v>
       </c>
       <c r="M108" s="1"/>
       <c r="N108" s="1"/>
@@ -13422,26 +13858,22 @@
         <v>10</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>16</v>
+        <v>621</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>636</v>
-      </c>
-      <c r="E109" s="1"/>
-      <c r="F109" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="G109" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H109" t="s">
-        <v>637</v>
-      </c>
+        <v>623</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>733</v>
+      </c>
+      <c r="F109" s="1"/>
+      <c r="G109" s="1"/>
+      <c r="H109" s="1"/>
       <c r="I109" s="1"/>
       <c r="J109" s="1"/>
       <c r="K109" s="1"/>
       <c r="L109" s="1" t="s">
-        <v>3</v>
+        <v>627</v>
       </c>
       <c r="M109" s="1"/>
       <c r="N109" s="1"/>
@@ -13453,19 +13885,22 @@
         <v>10</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>16</v>
+        <v>579</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>638</v>
-      </c>
-      <c r="E110" s="1"/>
+        <v>624</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>734</v>
+      </c>
       <c r="F110" s="1"/>
       <c r="G110" s="1"/>
+      <c r="H110" s="1"/>
       <c r="I110" s="1"/>
       <c r="J110" s="1"/>
       <c r="K110" s="1"/>
       <c r="L110" s="1" t="s">
-        <v>3</v>
+        <v>115</v>
       </c>
       <c r="M110" s="1"/>
       <c r="N110" s="1"/>
@@ -13477,22 +13912,22 @@
         <v>10</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>9</v>
+        <v>579</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>639</v>
-      </c>
-      <c r="E111" s="1"/>
-      <c r="F111" s="1" t="s">
-        <v>52</v>
-      </c>
+        <v>625</v>
+      </c>
+      <c r="E111" s="1" t="s">
+        <v>735</v>
+      </c>
+      <c r="F111" s="1"/>
       <c r="G111" s="1"/>
       <c r="H111" s="1"/>
       <c r="I111" s="1"/>
       <c r="J111" s="1"/>
       <c r="K111" s="1"/>
       <c r="L111" s="1" t="s">
-        <v>3</v>
+        <v>115</v>
       </c>
       <c r="M111" s="1"/>
       <c r="N111" s="1"/>
@@ -13504,26 +13939,22 @@
         <v>10</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>9</v>
+        <v>582</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>640</v>
-      </c>
-      <c r="E112" s="1"/>
-      <c r="F112" s="1" t="s">
-        <v>559</v>
-      </c>
-      <c r="G112" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H112" s="1" t="s">
-        <v>557</v>
-      </c>
+        <v>626</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>736</v>
+      </c>
+      <c r="F112" s="1"/>
+      <c r="G112" s="1"/>
+      <c r="H112" s="1"/>
       <c r="I112" s="1"/>
       <c r="J112" s="1"/>
       <c r="K112" s="1"/>
       <c r="L112" s="1" t="s">
-        <v>3</v>
+        <v>115</v>
       </c>
       <c r="M112" s="1"/>
       <c r="N112" s="1"/>
@@ -13532,20 +13963,25 @@
     </row>
     <row r="113" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B113" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C113" s="1"/>
-      <c r="D113" s="1"/>
-      <c r="E113" s="1"/>
+        <v>10</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="E113" s="1" t="s">
+        <v>737</v>
+      </c>
       <c r="F113" s="1"/>
       <c r="G113" s="1"/>
-      <c r="H113" s="1"/>
-      <c r="I113" s="1" t="s">
-        <v>154</v>
-      </c>
+      <c r="I113" s="1"/>
       <c r="J113" s="1"/>
       <c r="K113" s="1"/>
-      <c r="L113" s="1"/>
+      <c r="L113" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="M113" s="1"/>
       <c r="N113" s="1"/>
       <c r="O113" s="1"/>
@@ -13553,41 +13989,53 @@
     </row>
     <row r="114" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B114" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C114" s="1"/>
-      <c r="D114" s="1"/>
-      <c r="E114" s="1"/>
+        <v>10</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="E114" s="1" t="s">
+        <v>738</v>
+      </c>
       <c r="F114" s="1"/>
       <c r="G114" s="1"/>
       <c r="H114" s="1"/>
       <c r="I114" s="1"/>
       <c r="J114" s="1"/>
       <c r="K114" s="1"/>
-      <c r="L114" s="1"/>
+      <c r="L114" s="1" t="s">
+        <v>115</v>
+      </c>
       <c r="M114" s="1"/>
       <c r="N114" s="1"/>
       <c r="O114" s="1"/>
-      <c r="P114" s="1" t="s">
-        <v>546</v>
-      </c>
+      <c r="P114" s="1"/>
     </row>
     <row r="115" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B115" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="C115" s="1"/>
-      <c r="D115" s="1"/>
-      <c r="E115" s="1"/>
+        <v>10</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="E115" s="1" t="s">
+        <v>739</v>
+      </c>
       <c r="F115" s="1"/>
       <c r="G115" s="1"/>
       <c r="H115" s="1"/>
-      <c r="I115" s="1" t="s">
-        <v>545</v>
-      </c>
+      <c r="I115" s="1"/>
       <c r="J115" s="1"/>
       <c r="K115" s="1"/>
-      <c r="L115" s="1"/>
+      <c r="L115" s="1" t="s">
+        <v>115</v>
+      </c>
       <c r="M115" s="1"/>
       <c r="N115" s="1"/>
       <c r="O115" s="1"/>
@@ -13601,11 +14049,20 @@
         <v>16</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>621</v>
-      </c>
-      <c r="E116" s="1"/>
-      <c r="F116" s="1"/>
-      <c r="G116" s="1"/>
+        <v>630</v>
+      </c>
+      <c r="E116" s="1" t="s">
+        <v>740</v>
+      </c>
+      <c r="F116" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="G116" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H116" t="s">
+        <v>631</v>
+      </c>
       <c r="I116" s="1"/>
       <c r="J116" s="1"/>
       <c r="K116" s="1"/>
@@ -13625,9 +14082,11 @@
         <v>16</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>644</v>
-      </c>
-      <c r="E117" s="1"/>
+        <v>632</v>
+      </c>
+      <c r="E117" s="1" t="s">
+        <v>741</v>
+      </c>
       <c r="F117" s="1"/>
       <c r="G117" s="1"/>
       <c r="I117" s="1"/>
@@ -13642,22 +14101,29 @@
       <c r="P117" s="1"/>
     </row>
     <row r="118" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A118" s="8"/>
       <c r="B118" s="1" t="s">
-        <v>614</v>
-      </c>
-      <c r="C118" s="1"/>
-      <c r="D118" s="1"/>
-      <c r="E118" s="1"/>
-      <c r="F118" s="1"/>
+        <v>10</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="E118" s="1" t="s">
+        <v>742</v>
+      </c>
+      <c r="F118" s="1" t="s">
+        <v>52</v>
+      </c>
       <c r="G118" s="1"/>
       <c r="H118" s="1"/>
-      <c r="I118" s="1" t="s">
-        <v>645</v>
-      </c>
+      <c r="I118" s="1"/>
       <c r="J118" s="1"/>
       <c r="K118" s="1"/>
-      <c r="L118" s="1"/>
+      <c r="L118" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="M118" s="1"/>
       <c r="N118" s="1"/>
       <c r="O118" s="1"/>
@@ -13665,37 +14131,49 @@
     </row>
     <row r="119" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B119" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="C119" s="1"/>
-      <c r="D119" s="1"/>
-      <c r="E119" s="1"/>
-      <c r="F119" s="1"/>
-      <c r="G119" s="1"/>
-      <c r="H119" s="1"/>
-      <c r="I119" s="1" t="s">
-        <v>545</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>634</v>
+      </c>
+      <c r="E119" s="1" t="s">
+        <v>743</v>
+      </c>
+      <c r="F119" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="G119" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H119" s="1" t="s">
+        <v>782</v>
+      </c>
+      <c r="I119" s="1"/>
       <c r="J119" s="1"/>
       <c r="K119" s="1"/>
-      <c r="L119" s="1"/>
+      <c r="L119" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="M119" s="1"/>
       <c r="N119" s="1"/>
       <c r="O119" s="1"/>
       <c r="P119" s="1"/>
     </row>
     <row r="120" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A120" s="8"/>
       <c r="B120" s="1" t="s">
-        <v>646</v>
+        <v>2</v>
       </c>
       <c r="C120" s="1"/>
       <c r="D120" s="1"/>
       <c r="E120" s="1"/>
       <c r="F120" s="1"/>
       <c r="G120" s="1"/>
+      <c r="H120" s="1"/>
       <c r="I120" s="1" t="s">
-        <v>647</v>
+        <v>154</v>
       </c>
       <c r="J120" s="1"/>
       <c r="K120" s="1"/>
@@ -13707,14 +14185,10 @@
     </row>
     <row r="121" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B121" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C121" s="1" t="s">
-        <v>582</v>
-      </c>
-      <c r="D121" s="1" t="s">
-        <v>641</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="C121" s="1"/>
+      <c r="D121" s="1"/>
       <c r="E121" s="1"/>
       <c r="F121" s="1"/>
       <c r="G121" s="1"/>
@@ -13722,34 +14196,30 @@
       <c r="I121" s="1"/>
       <c r="J121" s="1"/>
       <c r="K121" s="1"/>
-      <c r="L121" s="1" t="s">
-        <v>115</v>
-      </c>
+      <c r="L121" s="1"/>
       <c r="M121" s="1"/>
       <c r="N121" s="1"/>
       <c r="O121" s="1"/>
-      <c r="P121" s="1"/>
+      <c r="P121" s="1" t="s">
+        <v>672</v>
+      </c>
     </row>
     <row r="122" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B122" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C122" s="1" t="s">
-        <v>582</v>
-      </c>
-      <c r="D122" s="1" t="s">
-        <v>642</v>
-      </c>
+        <v>547</v>
+      </c>
+      <c r="C122" s="1"/>
+      <c r="D122" s="1"/>
       <c r="E122" s="1"/>
       <c r="F122" s="1"/>
       <c r="G122" s="1"/>
       <c r="H122" s="1"/>
-      <c r="I122" s="1"/>
+      <c r="I122" s="1" t="s">
+        <v>545</v>
+      </c>
       <c r="J122" s="1"/>
       <c r="K122" s="1"/>
-      <c r="L122" s="1" t="s">
-        <v>115</v>
-      </c>
+      <c r="L122" s="1"/>
       <c r="M122" s="1"/>
       <c r="N122" s="1"/>
       <c r="O122" s="1"/>
@@ -13760,20 +14230,21 @@
         <v>10</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>582</v>
+        <v>16</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>643</v>
-      </c>
-      <c r="E123" s="1"/>
+        <v>615</v>
+      </c>
+      <c r="E123" s="1" t="s">
+        <v>744</v>
+      </c>
       <c r="F123" s="1"/>
       <c r="G123" s="1"/>
-      <c r="H123" s="1"/>
       <c r="I123" s="1"/>
       <c r="J123" s="1"/>
       <c r="K123" s="1"/>
       <c r="L123" s="1" t="s">
-        <v>115</v>
+        <v>3</v>
       </c>
       <c r="M123" s="1"/>
       <c r="N123" s="1"/>
@@ -13788,9 +14259,11 @@
         <v>16</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>648</v>
-      </c>
-      <c r="E124" s="1"/>
+        <v>638</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>745</v>
+      </c>
       <c r="F124" s="1"/>
       <c r="G124" s="1"/>
       <c r="I124" s="1"/>
@@ -13805,8 +14278,9 @@
       <c r="P124" s="1"/>
     </row>
     <row r="125" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A125" s="8"/>
       <c r="B125" s="1" t="s">
-        <v>2</v>
+        <v>608</v>
       </c>
       <c r="C125" s="1"/>
       <c r="D125" s="1"/>
@@ -13815,21 +14289,19 @@
       <c r="G125" s="1"/>
       <c r="H125" s="1"/>
       <c r="I125" s="1" t="s">
-        <v>109</v>
+        <v>639</v>
       </c>
       <c r="J125" s="1"/>
       <c r="K125" s="1"/>
       <c r="L125" s="1"/>
       <c r="M125" s="1"/>
       <c r="N125" s="1"/>
-      <c r="O125" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="O125" s="1"/>
       <c r="P125" s="1"/>
     </row>
     <row r="126" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B126" s="1" t="s">
-        <v>59</v>
+        <v>547</v>
       </c>
       <c r="C126" s="1"/>
       <c r="D126" s="1"/>
@@ -13837,54 +14309,60 @@
       <c r="F126" s="1"/>
       <c r="G126" s="1"/>
       <c r="H126" s="1"/>
-      <c r="I126" s="1"/>
+      <c r="I126" s="1" t="s">
+        <v>545</v>
+      </c>
       <c r="J126" s="1"/>
       <c r="K126" s="1"/>
       <c r="L126" s="1"/>
       <c r="M126" s="1"/>
       <c r="N126" s="1"/>
       <c r="O126" s="1"/>
-      <c r="P126" s="1" t="s">
-        <v>546</v>
-      </c>
+      <c r="P126" s="1"/>
     </row>
     <row r="127" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A127" s="8"/>
       <c r="B127" s="1" t="s">
-        <v>108</v>
+        <v>640</v>
       </c>
       <c r="C127" s="1"/>
       <c r="D127" s="1"/>
       <c r="E127" s="1"/>
       <c r="F127" s="1"/>
       <c r="G127" s="1"/>
-      <c r="H127" s="1"/>
-      <c r="I127" s="1"/>
+      <c r="I127" s="1" t="s">
+        <v>641</v>
+      </c>
       <c r="J127" s="1"/>
       <c r="K127" s="1"/>
       <c r="L127" s="1"/>
       <c r="M127" s="1"/>
-      <c r="N127" s="1" t="s">
-        <v>265</v>
-      </c>
+      <c r="N127" s="1"/>
       <c r="O127" s="1"/>
       <c r="P127" s="1"/>
     </row>
     <row r="128" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B128" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="C128" s="1"/>
-      <c r="D128" s="1"/>
-      <c r="E128" s="1"/>
+        <v>10</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="D128" s="1" t="s">
+        <v>635</v>
+      </c>
+      <c r="E128" s="1" t="s">
+        <v>746</v>
+      </c>
       <c r="F128" s="1"/>
       <c r="G128" s="1"/>
       <c r="H128" s="1"/>
-      <c r="I128" s="1" t="s">
-        <v>545</v>
-      </c>
+      <c r="I128" s="1"/>
       <c r="J128" s="1"/>
       <c r="K128" s="1"/>
-      <c r="L128" s="1"/>
+      <c r="L128" s="1" t="s">
+        <v>115</v>
+      </c>
       <c r="M128" s="1"/>
       <c r="N128" s="1"/>
       <c r="O128" s="1"/>
@@ -13895,26 +14373,22 @@
         <v>10</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>679</v>
+        <v>579</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>649</v>
-      </c>
-      <c r="E129" s="1"/>
-      <c r="F129" s="1" t="s">
-        <v>559</v>
-      </c>
-      <c r="G129" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H129" s="1" t="s">
-        <v>650</v>
-      </c>
+        <v>636</v>
+      </c>
+      <c r="E129" s="1" t="s">
+        <v>747</v>
+      </c>
+      <c r="F129" s="1"/>
+      <c r="G129" s="1"/>
+      <c r="H129" s="1"/>
       <c r="I129" s="1"/>
       <c r="J129" s="1"/>
       <c r="K129" s="1"/>
       <c r="L129" s="1" t="s">
-        <v>3</v>
+        <v>115</v>
       </c>
       <c r="M129" s="1"/>
       <c r="N129" s="1"/>
@@ -13926,26 +14400,22 @@
         <v>10</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>24</v>
+        <v>579</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>651</v>
-      </c>
-      <c r="E130" s="1"/>
-      <c r="F130" s="1" t="s">
-        <v>560</v>
-      </c>
-      <c r="G130" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H130" s="1" t="s">
-        <v>652</v>
-      </c>
+        <v>637</v>
+      </c>
+      <c r="E130" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="F130" s="1"/>
+      <c r="G130" s="1"/>
+      <c r="H130" s="1"/>
       <c r="I130" s="1"/>
       <c r="J130" s="1"/>
       <c r="K130" s="1"/>
       <c r="L130" s="1" t="s">
-        <v>3</v>
+        <v>115</v>
       </c>
       <c r="M130" s="1"/>
       <c r="N130" s="1"/>
@@ -13960,18 +14430,13 @@
         <v>16</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="E131" s="1"/>
-      <c r="F131" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="G131" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H131" t="s">
-        <v>654</v>
-      </c>
+        <v>642</v>
+      </c>
+      <c r="E131" s="1" t="s">
+        <v>749</v>
+      </c>
+      <c r="F131" s="1"/>
+      <c r="G131" s="1"/>
       <c r="I131" s="1"/>
       <c r="J131" s="1"/>
       <c r="K131" s="1"/>
@@ -13985,45 +14450,33 @@
     </row>
     <row r="132" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B132" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C132" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D132" s="1" t="s">
-        <v>655</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="C132" s="1"/>
+      <c r="D132" s="1"/>
       <c r="E132" s="1"/>
-      <c r="F132" s="1" t="s">
-        <v>560</v>
-      </c>
-      <c r="G132" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H132" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I132" s="1"/>
+      <c r="F132" s="1"/>
+      <c r="G132" s="1"/>
+      <c r="H132" s="1"/>
+      <c r="I132" s="1" t="s">
+        <v>109</v>
+      </c>
       <c r="J132" s="1"/>
       <c r="K132" s="1"/>
-      <c r="L132" s="1" t="s">
-        <v>3</v>
-      </c>
+      <c r="L132" s="1"/>
       <c r="M132" s="1"/>
       <c r="N132" s="1"/>
-      <c r="O132" s="1"/>
+      <c r="O132" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="P132" s="1"/>
     </row>
     <row r="133" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B133" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C133" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D133" s="1" t="s">
-        <v>656</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="C133" s="1"/>
+      <c r="D133" s="1"/>
       <c r="E133" s="1"/>
       <c r="F133" s="1"/>
       <c r="G133" s="1"/>
@@ -14031,71 +14484,53 @@
       <c r="I133" s="1"/>
       <c r="J133" s="1"/>
       <c r="K133" s="1"/>
-      <c r="L133" s="1" t="s">
-        <v>3</v>
-      </c>
+      <c r="L133" s="1"/>
       <c r="M133" s="1"/>
       <c r="N133" s="1"/>
       <c r="O133" s="1"/>
-      <c r="P133" s="1"/>
+      <c r="P133" s="1" t="s">
+        <v>546</v>
+      </c>
     </row>
     <row r="134" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B134" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C134" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D134" s="1" t="s">
-        <v>657</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="C134" s="1"/>
+      <c r="D134" s="1"/>
       <c r="E134" s="1"/>
-      <c r="F134" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="G134" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H134" t="s">
-        <v>658</v>
-      </c>
+      <c r="F134" s="1"/>
+      <c r="G134" s="1"/>
+      <c r="H134" s="1"/>
       <c r="I134" s="1"/>
       <c r="J134" s="1"/>
       <c r="K134" s="1"/>
-      <c r="L134" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M134" s="1"/>
-      <c r="N134" s="1"/>
+      <c r="L134" s="1"/>
+      <c r="M134" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="N134" s="1" t="s">
+        <v>106</v>
+      </c>
       <c r="O134" s="1"/>
       <c r="P134" s="1"/>
     </row>
     <row r="135" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B135" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C135" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D135" s="1" t="s">
-        <v>659</v>
-      </c>
+        <v>547</v>
+      </c>
+      <c r="C135" s="1"/>
+      <c r="D135" s="1"/>
       <c r="E135" s="1"/>
-      <c r="F135" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="G135" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H135" t="s">
-        <v>660</v>
-      </c>
-      <c r="I135" s="1"/>
+      <c r="F135" s="1"/>
+      <c r="G135" s="1"/>
+      <c r="H135" s="1"/>
+      <c r="I135" s="1" t="s">
+        <v>545</v>
+      </c>
       <c r="J135" s="1"/>
       <c r="K135" s="1"/>
-      <c r="L135" s="1" t="s">
-        <v>3</v>
-      </c>
+      <c r="L135" s="1"/>
       <c r="M135" s="1"/>
       <c r="N135" s="1"/>
       <c r="O135" s="1"/>
@@ -14106,20 +14541,28 @@
         <v>10</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>91</v>
+        <v>671</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>661</v>
-      </c>
-      <c r="E136" s="1"/>
-      <c r="F136" s="1"/>
-      <c r="G136" s="1"/>
-      <c r="H136" s="1"/>
+        <v>643</v>
+      </c>
+      <c r="E136" s="1" t="s">
+        <v>750</v>
+      </c>
+      <c r="F136" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="G136" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H136" s="1" t="s">
+        <v>644</v>
+      </c>
       <c r="I136" s="1"/>
       <c r="J136" s="1"/>
       <c r="K136" s="1"/>
       <c r="L136" s="1" t="s">
-        <v>88</v>
+        <v>3</v>
       </c>
       <c r="M136" s="1"/>
       <c r="N136" s="1"/>
@@ -14131,20 +14574,22 @@
         <v>10</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>662</v>
-      </c>
-      <c r="E137" s="1"/>
+        <v>645</v>
+      </c>
+      <c r="E137" s="1" t="s">
+        <v>751</v>
+      </c>
       <c r="F137" s="1" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="G137" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H137" s="1" t="s">
-        <v>543</v>
+        <v>646</v>
       </c>
       <c r="I137" s="1"/>
       <c r="J137" s="1"/>
@@ -14162,15 +14607,23 @@
         <v>10</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>663</v>
-      </c>
-      <c r="E138" s="1"/>
-      <c r="F138" s="1"/>
-      <c r="G138" s="1"/>
-      <c r="H138" s="1"/>
+        <v>647</v>
+      </c>
+      <c r="E138" s="1" t="s">
+        <v>752</v>
+      </c>
+      <c r="F138" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="G138" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H138" t="s">
+        <v>648</v>
+      </c>
       <c r="I138" s="1"/>
       <c r="J138" s="1"/>
       <c r="K138" s="1"/>
@@ -14187,20 +14640,22 @@
         <v>10</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>664</v>
-      </c>
-      <c r="E139" s="1"/>
+        <v>649</v>
+      </c>
+      <c r="E139" s="1" t="s">
+        <v>753</v>
+      </c>
       <c r="F139" s="1" t="s">
-        <v>294</v>
+        <v>558</v>
       </c>
       <c r="G139" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H139" t="s">
-        <v>665</v>
+        <v>20</v>
+      </c>
+      <c r="H139" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="I139" s="1"/>
       <c r="J139" s="1"/>
@@ -14218,21 +14673,17 @@
         <v>10</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>666</v>
-      </c>
-      <c r="E140" s="1"/>
-      <c r="F140" s="1" t="s">
-        <v>559</v>
-      </c>
-      <c r="G140" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H140" s="1" t="s">
-        <v>542</v>
-      </c>
+        <v>650</v>
+      </c>
+      <c r="E140" s="1" t="s">
+        <v>754</v>
+      </c>
+      <c r="F140" s="1"/>
+      <c r="G140" s="1"/>
+      <c r="H140" s="1"/>
       <c r="I140" s="1"/>
       <c r="J140" s="1"/>
       <c r="K140" s="1"/>
@@ -14249,15 +14700,23 @@
         <v>10</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>667</v>
-      </c>
-      <c r="E141" s="1"/>
-      <c r="F141" s="1"/>
-      <c r="G141" s="1"/>
-      <c r="H141" s="1"/>
+        <v>651</v>
+      </c>
+      <c r="E141" s="1" t="s">
+        <v>755</v>
+      </c>
+      <c r="F141" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="G141" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H141" t="s">
+        <v>783</v>
+      </c>
       <c r="I141" s="1"/>
       <c r="J141" s="1"/>
       <c r="K141" s="1"/>
@@ -14274,15 +14733,23 @@
         <v>10</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>668</v>
-      </c>
-      <c r="E142" s="1"/>
-      <c r="F142" s="1"/>
-      <c r="G142" s="1"/>
-      <c r="H142" s="1"/>
+        <v>652</v>
+      </c>
+      <c r="E142" s="1" t="s">
+        <v>756</v>
+      </c>
+      <c r="F142" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="G142" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H142" t="s">
+        <v>653</v>
+      </c>
       <c r="I142" s="1"/>
       <c r="J142" s="1"/>
       <c r="K142" s="1"/>
@@ -14302,12 +14769,12 @@
         <v>91</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>669</v>
-      </c>
-      <c r="E143" s="1"/>
-      <c r="F143" s="1" t="s">
-        <v>52</v>
-      </c>
+        <v>654</v>
+      </c>
+      <c r="E143" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="F143" s="1"/>
       <c r="G143" s="1"/>
       <c r="H143" s="1"/>
       <c r="I143" s="1"/>
@@ -14326,20 +14793,22 @@
         <v>10</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>670</v>
-      </c>
-      <c r="E144" s="1"/>
+        <v>655</v>
+      </c>
+      <c r="E144" s="1" t="s">
+        <v>758</v>
+      </c>
       <c r="F144" s="1" t="s">
-        <v>294</v>
+        <v>557</v>
       </c>
       <c r="G144" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H144" t="s">
-        <v>527</v>
+        <v>12</v>
+      </c>
+      <c r="H144" s="1" t="s">
+        <v>543</v>
       </c>
       <c r="I144" s="1"/>
       <c r="J144" s="1"/>
@@ -14357,12 +14826,14 @@
         <v>10</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>91</v>
+        <v>9</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>671</v>
-      </c>
-      <c r="E145" s="1"/>
+        <v>656</v>
+      </c>
+      <c r="E145" s="1" t="s">
+        <v>759</v>
+      </c>
       <c r="F145" s="1"/>
       <c r="G145" s="1"/>
       <c r="H145" s="1"/>
@@ -14370,7 +14841,7 @@
       <c r="J145" s="1"/>
       <c r="K145" s="1"/>
       <c r="L145" s="1" t="s">
-        <v>88</v>
+        <v>3</v>
       </c>
       <c r="M145" s="1"/>
       <c r="N145" s="1"/>
@@ -14385,17 +14856,19 @@
         <v>16</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>672</v>
-      </c>
-      <c r="E146" s="1"/>
+        <v>657</v>
+      </c>
+      <c r="E146" s="1" t="s">
+        <v>760</v>
+      </c>
       <c r="F146" s="1" t="s">
         <v>294</v>
       </c>
       <c r="G146" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H146" t="s">
-        <v>673</v>
+        <v>658</v>
       </c>
       <c r="I146" s="1"/>
       <c r="J146" s="1"/>
@@ -14413,20 +14886,28 @@
         <v>10</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>91</v>
+        <v>9</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>674</v>
-      </c>
-      <c r="E147" s="1"/>
-      <c r="F147" s="1"/>
-      <c r="G147" s="1"/>
-      <c r="H147" s="1"/>
+        <v>659</v>
+      </c>
+      <c r="E147" s="1" t="s">
+        <v>761</v>
+      </c>
+      <c r="F147" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="G147" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H147" s="1" t="s">
+        <v>542</v>
+      </c>
       <c r="I147" s="1"/>
       <c r="J147" s="1"/>
       <c r="K147" s="1"/>
       <c r="L147" s="1" t="s">
-        <v>88</v>
+        <v>3</v>
       </c>
       <c r="M147" s="1"/>
       <c r="N147" s="1"/>
@@ -14435,41 +14916,53 @@
     </row>
     <row r="148" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B148" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C148" s="1"/>
-      <c r="D148" s="1"/>
-      <c r="E148" s="1"/>
+        <v>10</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D148" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="E148" s="1" t="s">
+        <v>762</v>
+      </c>
       <c r="F148" s="1"/>
       <c r="G148" s="1"/>
       <c r="H148" s="1"/>
       <c r="I148" s="1"/>
       <c r="J148" s="1"/>
       <c r="K148" s="1"/>
-      <c r="L148" s="1"/>
-      <c r="M148" s="1" t="s">
-        <v>110</v>
-      </c>
+      <c r="L148" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M148" s="1"/>
       <c r="N148" s="1"/>
       <c r="O148" s="1"/>
       <c r="P148" s="1"/>
     </row>
     <row r="149" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B149" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C149" s="1"/>
-      <c r="D149" s="1"/>
-      <c r="E149" s="1"/>
+        <v>10</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D149" s="1" t="s">
+        <v>661</v>
+      </c>
+      <c r="E149" s="1" t="s">
+        <v>763</v>
+      </c>
       <c r="F149" s="1"/>
       <c r="G149" s="1"/>
       <c r="H149" s="1"/>
-      <c r="I149" s="1" t="s">
-        <v>604</v>
-      </c>
+      <c r="I149" s="1"/>
       <c r="J149" s="1"/>
       <c r="K149" s="1"/>
-      <c r="L149" s="1"/>
+      <c r="L149" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="M149" s="1"/>
       <c r="N149" s="1"/>
       <c r="O149" s="1"/>
@@ -14477,41 +14970,61 @@
     </row>
     <row r="150" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B150" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C150" s="1"/>
-      <c r="D150" s="1"/>
-      <c r="E150" s="1"/>
-      <c r="F150" s="1"/>
+        <v>10</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D150" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="E150" s="1" t="s">
+        <v>764</v>
+      </c>
+      <c r="F150" s="1" t="s">
+        <v>52</v>
+      </c>
       <c r="G150" s="1"/>
       <c r="H150" s="1"/>
       <c r="I150" s="1"/>
       <c r="J150" s="1"/>
       <c r="K150" s="1"/>
-      <c r="L150" s="1"/>
+      <c r="L150" s="1" t="s">
+        <v>88</v>
+      </c>
       <c r="M150" s="1"/>
       <c r="N150" s="1"/>
       <c r="O150" s="1"/>
-      <c r="P150" s="1" t="s">
-        <v>546</v>
-      </c>
+      <c r="P150" s="1"/>
     </row>
     <row r="151" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B151" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="C151" s="1"/>
-      <c r="D151" s="1"/>
-      <c r="E151" s="1"/>
-      <c r="F151" s="1"/>
-      <c r="G151" s="1"/>
-      <c r="H151" s="1"/>
-      <c r="I151" s="1" t="s">
-        <v>545</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D151" s="1" t="s">
+        <v>663</v>
+      </c>
+      <c r="E151" s="1" t="s">
+        <v>765</v>
+      </c>
+      <c r="F151" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="G151" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H151" t="s">
+        <v>527</v>
+      </c>
+      <c r="I151" s="1"/>
       <c r="J151" s="1"/>
       <c r="K151" s="1"/>
-      <c r="L151" s="1"/>
+      <c r="L151" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="M151" s="1"/>
       <c r="N151" s="1"/>
       <c r="O151" s="1"/>
@@ -14522,26 +15035,22 @@
         <v>10</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>24</v>
+        <v>91</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>675</v>
-      </c>
-      <c r="E152" s="1"/>
-      <c r="F152" s="1" t="s">
-        <v>560</v>
-      </c>
-      <c r="G152" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H152" s="1" t="s">
-        <v>676</v>
-      </c>
+        <v>664</v>
+      </c>
+      <c r="E152" s="1" t="s">
+        <v>766</v>
+      </c>
+      <c r="F152" s="1"/>
+      <c r="G152" s="1"/>
+      <c r="H152" s="1"/>
       <c r="I152" s="1"/>
       <c r="J152" s="1"/>
       <c r="K152" s="1"/>
       <c r="L152" s="1" t="s">
-        <v>3</v>
+        <v>88</v>
       </c>
       <c r="M152" s="1"/>
       <c r="N152" s="1"/>
@@ -14553,20 +15062,22 @@
         <v>10</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>677</v>
-      </c>
-      <c r="E153" s="1"/>
+        <v>665</v>
+      </c>
+      <c r="E153" s="1" t="s">
+        <v>767</v>
+      </c>
       <c r="F153" s="1" t="s">
-        <v>559</v>
+        <v>294</v>
       </c>
       <c r="G153" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H153" s="1" t="s">
-        <v>678</v>
+        <v>20</v>
+      </c>
+      <c r="H153" t="s">
+        <v>666</v>
       </c>
       <c r="I153" s="1"/>
       <c r="J153" s="1"/>
@@ -14581,29 +15092,35 @@
     </row>
     <row r="154" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B154" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C154" s="1"/>
-      <c r="D154" s="1"/>
-      <c r="E154" s="1"/>
+        <v>10</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D154" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="E154" s="1" t="s">
+        <v>768</v>
+      </c>
       <c r="F154" s="1"/>
       <c r="G154" s="1"/>
       <c r="H154" s="1"/>
-      <c r="I154" s="1" t="s">
-        <v>517</v>
-      </c>
+      <c r="I154" s="1"/>
       <c r="J154" s="1"/>
       <c r="K154" s="1"/>
-      <c r="L154" s="1"/>
+      <c r="L154" s="1" t="s">
+        <v>88</v>
+      </c>
       <c r="M154" s="1"/>
       <c r="N154" s="1"/>
-      <c r="O154" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="O154" s="1"/>
       <c r="P154" s="1"/>
     </row>
     <row r="155" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B155" s="1"/>
+      <c r="B155" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="C155" s="1"/>
       <c r="D155" s="1"/>
       <c r="E155" s="1"/>
@@ -14614,20 +15131,26 @@
       <c r="J155" s="1"/>
       <c r="K155" s="1"/>
       <c r="L155" s="1"/>
-      <c r="M155" s="1"/>
+      <c r="M155" s="1" t="s">
+        <v>110</v>
+      </c>
       <c r="N155" s="1"/>
       <c r="O155" s="1"/>
       <c r="P155" s="1"/>
     </row>
     <row r="156" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B156" s="1"/>
+      <c r="B156" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="C156" s="1"/>
       <c r="D156" s="1"/>
       <c r="E156" s="1"/>
       <c r="F156" s="1"/>
       <c r="G156" s="1"/>
       <c r="H156" s="1"/>
-      <c r="I156" s="1"/>
+      <c r="I156" s="1" t="s">
+        <v>600</v>
+      </c>
       <c r="J156" s="1"/>
       <c r="K156" s="1"/>
       <c r="L156" s="1"/>
@@ -14637,7 +15160,9 @@
       <c r="P156" s="1"/>
     </row>
     <row r="157" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B157" s="1"/>
+      <c r="B157" s="1" t="s">
+        <v>59</v>
+      </c>
       <c r="C157" s="1"/>
       <c r="D157" s="1"/>
       <c r="E157" s="1"/>
@@ -14651,17 +15176,23 @@
       <c r="M157" s="1"/>
       <c r="N157" s="1"/>
       <c r="O157" s="1"/>
-      <c r="P157" s="1"/>
+      <c r="P157" s="1" t="s">
+        <v>546</v>
+      </c>
     </row>
     <row r="158" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B158" s="1"/>
+      <c r="B158" s="1" t="s">
+        <v>547</v>
+      </c>
       <c r="C158" s="1"/>
       <c r="D158" s="1"/>
       <c r="E158" s="1"/>
       <c r="F158" s="1"/>
       <c r="G158" s="1"/>
       <c r="H158" s="1"/>
-      <c r="I158" s="1"/>
+      <c r="I158" s="1" t="s">
+        <v>545</v>
+      </c>
       <c r="J158" s="1"/>
       <c r="K158" s="1"/>
       <c r="L158" s="1"/>
@@ -14671,54 +15202,92 @@
       <c r="P158" s="1"/>
     </row>
     <row r="159" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B159" s="1"/>
-      <c r="C159" s="1"/>
-      <c r="D159" s="1"/>
-      <c r="E159" s="1"/>
-      <c r="F159" s="1"/>
-      <c r="G159" s="1"/>
-      <c r="H159" s="1"/>
+      <c r="B159" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D159" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="E159" s="1" t="s">
+        <v>769</v>
+      </c>
+      <c r="F159" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="G159" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H159" s="1" t="s">
+        <v>784</v>
+      </c>
       <c r="I159" s="1"/>
       <c r="J159" s="1"/>
       <c r="K159" s="1"/>
-      <c r="L159" s="1"/>
+      <c r="L159" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="M159" s="1"/>
       <c r="N159" s="1"/>
       <c r="O159" s="1"/>
       <c r="P159" s="1"/>
     </row>
     <row r="160" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B160" s="1"/>
-      <c r="C160" s="1"/>
-      <c r="D160" s="1"/>
-      <c r="E160" s="1"/>
-      <c r="F160" s="1"/>
-      <c r="G160" s="1"/>
-      <c r="H160" s="1"/>
+      <c r="B160" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D160" s="1" t="s">
+        <v>669</v>
+      </c>
+      <c r="E160" s="1" t="s">
+        <v>770</v>
+      </c>
+      <c r="F160" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="G160" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H160" s="1" t="s">
+        <v>670</v>
+      </c>
       <c r="I160" s="1"/>
       <c r="J160" s="1"/>
       <c r="K160" s="1"/>
-      <c r="L160" s="1"/>
+      <c r="L160" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="M160" s="1"/>
       <c r="N160" s="1"/>
       <c r="O160" s="1"/>
       <c r="P160" s="1"/>
     </row>
     <row r="161" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B161" s="1"/>
+      <c r="B161" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="C161" s="1"/>
       <c r="D161" s="1"/>
       <c r="E161" s="1"/>
       <c r="F161" s="1"/>
       <c r="G161" s="1"/>
       <c r="H161" s="1"/>
-      <c r="I161" s="1"/>
+      <c r="I161" s="1" t="s">
+        <v>517</v>
+      </c>
       <c r="J161" s="1"/>
       <c r="K161" s="1"/>
       <c r="L161" s="1"/>
       <c r="M161" s="1"/>
       <c r="N161" s="1"/>
-      <c r="O161" s="1"/>
+      <c r="O161" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="P161" s="1"/>
     </row>
     <row r="162" spans="2:16" x14ac:dyDescent="0.3">
@@ -14772,6 +15341,125 @@
       <c r="O164" s="1"/>
       <c r="P164" s="1"/>
     </row>
+    <row r="165" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B165" s="1"/>
+      <c r="C165" s="1"/>
+      <c r="D165" s="1"/>
+      <c r="E165" s="1"/>
+      <c r="F165" s="1"/>
+      <c r="G165" s="1"/>
+      <c r="H165" s="1"/>
+      <c r="I165" s="1"/>
+      <c r="J165" s="1"/>
+      <c r="K165" s="1"/>
+      <c r="L165" s="1"/>
+      <c r="M165" s="1"/>
+      <c r="N165" s="1"/>
+      <c r="O165" s="1"/>
+      <c r="P165" s="1"/>
+    </row>
+    <row r="166" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B166" s="1"/>
+      <c r="C166" s="1"/>
+      <c r="D166" s="1"/>
+      <c r="E166" s="1"/>
+      <c r="F166" s="1"/>
+      <c r="G166" s="1"/>
+      <c r="H166" s="1"/>
+      <c r="I166" s="1"/>
+      <c r="J166" s="1"/>
+      <c r="K166" s="1"/>
+      <c r="L166" s="1"/>
+      <c r="M166" s="1"/>
+      <c r="N166" s="1"/>
+      <c r="O166" s="1"/>
+      <c r="P166" s="1"/>
+    </row>
+    <row r="167" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B167" s="1"/>
+      <c r="C167" s="1"/>
+      <c r="D167" s="1"/>
+      <c r="E167" s="1"/>
+      <c r="F167" s="1"/>
+      <c r="G167" s="1"/>
+      <c r="H167" s="1"/>
+      <c r="I167" s="1"/>
+      <c r="J167" s="1"/>
+      <c r="K167" s="1"/>
+      <c r="L167" s="1"/>
+      <c r="M167" s="1"/>
+      <c r="N167" s="1"/>
+      <c r="O167" s="1"/>
+      <c r="P167" s="1"/>
+    </row>
+    <row r="168" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B168" s="1"/>
+      <c r="C168" s="1"/>
+      <c r="D168" s="1"/>
+      <c r="E168" s="1"/>
+      <c r="F168" s="1"/>
+      <c r="G168" s="1"/>
+      <c r="H168" s="1"/>
+      <c r="I168" s="1"/>
+      <c r="J168" s="1"/>
+      <c r="K168" s="1"/>
+      <c r="L168" s="1"/>
+      <c r="M168" s="1"/>
+      <c r="N168" s="1"/>
+      <c r="O168" s="1"/>
+      <c r="P168" s="1"/>
+    </row>
+    <row r="169" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B169" s="1"/>
+      <c r="C169" s="1"/>
+      <c r="D169" s="1"/>
+      <c r="E169" s="1"/>
+      <c r="F169" s="1"/>
+      <c r="G169" s="1"/>
+      <c r="H169" s="1"/>
+      <c r="I169" s="1"/>
+      <c r="J169" s="1"/>
+      <c r="K169" s="1"/>
+      <c r="L169" s="1"/>
+      <c r="M169" s="1"/>
+      <c r="N169" s="1"/>
+      <c r="O169" s="1"/>
+      <c r="P169" s="1"/>
+    </row>
+    <row r="170" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B170" s="1"/>
+      <c r="C170" s="1"/>
+      <c r="D170" s="1"/>
+      <c r="E170" s="1"/>
+      <c r="F170" s="1"/>
+      <c r="G170" s="1"/>
+      <c r="H170" s="1"/>
+      <c r="I170" s="1"/>
+      <c r="J170" s="1"/>
+      <c r="K170" s="1"/>
+      <c r="L170" s="1"/>
+      <c r="M170" s="1"/>
+      <c r="N170" s="1"/>
+      <c r="O170" s="1"/>
+      <c r="P170" s="1"/>
+    </row>
+    <row r="171" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B171" s="1"/>
+      <c r="C171" s="1"/>
+      <c r="D171" s="1"/>
+      <c r="E171" s="1"/>
+      <c r="F171" s="1"/>
+      <c r="G171" s="1"/>
+      <c r="H171" s="1"/>
+      <c r="I171" s="1"/>
+      <c r="J171" s="1"/>
+      <c r="K171" s="1"/>
+      <c r="L171" s="1"/>
+      <c r="M171" s="1"/>
+      <c r="N171" s="1"/>
+      <c r="O171" s="1"/>
+      <c r="P171" s="1"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/resource/Script/script_InertiaLucis.xlsx
+++ b/resource/Script/script_InertiaLucis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\usosctheater\resource\Script\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{120B64F0-3016-42BF-851C-B753A1CAC160}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{343E31F3-FA61-4022-9CA7-8120B913415D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="2" xr2:uid="{12160F34-6A21-4287-85A5-86880D8D3A1A}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2313" uniqueCount="789">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2314" uniqueCount="788">
   <si>
     <t>se_trans_out|se_trans_in</t>
   </si>
@@ -2147,22 +2147,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>eyeblink</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>TRANSITION</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>fadeout</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>1등 못하면 용서 안할거니까…</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>SNS에서 후유코쨩이 좋은 얼굴을 하고 있다고 화제가 되고 있슴다.</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -2670,6 +2654,18 @@
   </si>
   <si>
     <t>smile1 face_close3 lip_smile</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>… 1등 못하면 용서 안할거니까…</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>se_taoreru</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.4</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -2720,7 +2716,7 @@
       <charset val="129"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2736,12 +2732,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2792,7 +2782,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2818,9 +2808,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3302,7 +3289,7 @@
     </row>
     <row r="3" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -3312,7 +3299,7 @@
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
@@ -4170,7 +4157,7 @@
     </row>
     <row r="33" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B33" s="1" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
@@ -4180,7 +4167,7 @@
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
       <c r="J33" s="1" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
@@ -5355,7 +5342,7 @@
     </row>
     <row r="76" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B76" s="1" t="s">
-        <v>784</v>
+        <v>780</v>
       </c>
       <c r="C76" s="1"/>
       <c r="D76" s="1"/>
@@ -5365,7 +5352,7 @@
       <c r="H76" s="1"/>
       <c r="I76" s="1"/>
       <c r="J76" s="1" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
       <c r="K76" s="1"/>
       <c r="L76" s="1"/>
@@ -6493,7 +6480,7 @@
     </row>
     <row r="3" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -6503,7 +6490,7 @@
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
@@ -11139,7 +11126,7 @@
     </row>
     <row r="4" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
@@ -11149,12 +11136,12 @@
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
       <c r="M4" s="1" t="s">
-        <v>771</v>
+        <v>767</v>
       </c>
       <c r="N4" s="1" t="s">
         <v>106</v>
@@ -11194,7 +11181,7 @@
         <v>548</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>293</v>
@@ -11227,7 +11214,7 @@
         <v>549</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>556</v>
@@ -11236,7 +11223,7 @@
         <v>121</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
@@ -11260,7 +11247,7 @@
         <v>550</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>293</v>
@@ -11293,7 +11280,7 @@
         <v>553</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>52</v>
@@ -11343,7 +11330,7 @@
         <v>554</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>556</v>
@@ -11352,7 +11339,7 @@
         <v>121</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
@@ -11376,7 +11363,7 @@
         <v>555</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>293</v>
@@ -11385,7 +11372,7 @@
         <v>12</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
@@ -11409,7 +11396,7 @@
         <v>559</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>557</v>
@@ -11442,7 +11429,7 @@
         <v>560</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
@@ -11468,7 +11455,7 @@
         <v>561</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>293</v>
@@ -11501,7 +11488,7 @@
         <v>563</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>293</v>
@@ -11510,7 +11497,7 @@
         <v>12</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
@@ -11534,7 +11521,7 @@
         <v>564</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
@@ -11561,7 +11548,7 @@
         <v>565</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>557</v>
@@ -11594,7 +11581,7 @@
         <v>567</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>293</v>
@@ -11696,7 +11683,7 @@
         <v>569</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>293</v>
@@ -11729,7 +11716,7 @@
         <v>571</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
@@ -11756,7 +11743,7 @@
         <v>572</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>293</v>
@@ -11789,7 +11776,7 @@
         <v>573</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>557</v>
@@ -11798,7 +11785,7 @@
         <v>5</v>
       </c>
       <c r="H26" t="s">
-        <v>777</v>
+        <v>773</v>
       </c>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
@@ -11822,7 +11809,7 @@
         <v>574</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>695</v>
+        <v>691</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>293</v>
@@ -11960,7 +11947,7 @@
         <v>575</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>696</v>
+        <v>692</v>
       </c>
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
@@ -11987,7 +11974,7 @@
         <v>576</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
@@ -12014,7 +12001,7 @@
         <v>577</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
@@ -12071,12 +12058,12 @@
       <c r="N37" s="1"/>
       <c r="O37" s="1"/>
       <c r="P37" s="1" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
     </row>
     <row r="38" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B38" s="1" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
@@ -12086,12 +12073,12 @@
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
       <c r="J38" s="1" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
       <c r="K38" s="1"/>
       <c r="L38" s="1"/>
       <c r="M38" s="1" t="s">
-        <v>772</v>
+        <v>768</v>
       </c>
       <c r="N38" s="1" t="s">
         <v>106</v>
@@ -12101,7 +12088,7 @@
     </row>
     <row r="39" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B39" s="1" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
@@ -12110,7 +12097,7 @@
       <c r="G39" s="1"/>
       <c r="H39" s="1"/>
       <c r="I39" s="1" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="J39" s="1" t="s">
         <v>608</v>
@@ -12118,7 +12105,7 @@
       <c r="K39" s="1"/>
       <c r="L39" s="1"/>
       <c r="M39" s="1" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="N39" s="1" t="s">
         <v>106</v>
@@ -12158,7 +12145,7 @@
         <v>579</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
@@ -12219,7 +12206,7 @@
       <c r="N43" s="1"/>
       <c r="O43" s="1"/>
       <c r="P43" s="1" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
     </row>
     <row r="44" spans="2:16" x14ac:dyDescent="0.3">
@@ -12233,7 +12220,7 @@
         <v>580</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
@@ -12260,7 +12247,7 @@
         <v>582</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="F45" s="1"/>
       <c r="G45" s="1"/>
@@ -12287,7 +12274,7 @@
         <v>583</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
       <c r="F46" s="1"/>
       <c r="G46" s="1"/>
@@ -12314,7 +12301,7 @@
         <v>584</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="F47" s="1"/>
       <c r="G47" s="1"/>
@@ -12341,7 +12328,7 @@
         <v>585</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="F48" s="1"/>
       <c r="G48" s="1"/>
@@ -12368,7 +12355,7 @@
         <v>586</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="F49" s="1"/>
       <c r="G49" s="1"/>
@@ -12395,7 +12382,7 @@
         <v>587</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="F50" s="1"/>
       <c r="G50" s="1"/>
@@ -12422,7 +12409,7 @@
         <v>588</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="F51" s="1"/>
       <c r="G51" s="1"/>
@@ -12449,7 +12436,7 @@
         <v>589</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="F52" s="1"/>
       <c r="G52" s="1"/>
@@ -12476,7 +12463,7 @@
         <v>590</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="F53" s="1"/>
       <c r="G53" s="1"/>
@@ -12529,7 +12516,7 @@
       <c r="N55" s="1"/>
       <c r="O55" s="1"/>
       <c r="P55" s="1" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
     </row>
     <row r="56" spans="2:16" x14ac:dyDescent="0.3">
@@ -12561,10 +12548,10 @@
         <v>16</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>293</v>
@@ -12591,13 +12578,13 @@
         <v>10</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>592</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>52</v>
@@ -12620,13 +12607,13 @@
         <v>10</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>593</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="F59" s="1"/>
       <c r="G59" s="1"/>
@@ -12653,7 +12640,7 @@
         <v>594</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>293</v>
@@ -12686,7 +12673,7 @@
         <v>596</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>52</v>
@@ -12715,7 +12702,7 @@
         <v>597</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="F62" s="1"/>
       <c r="G62" s="1"/>
@@ -12742,7 +12729,7 @@
         <v>598</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>697</v>
+        <v>693</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>293</v>
@@ -12787,7 +12774,7 @@
     </row>
     <row r="65" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B65" s="1" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
       <c r="C65" s="1"/>
       <c r="D65" s="1"/>
@@ -12796,10 +12783,10 @@
       <c r="G65" s="1"/>
       <c r="H65" s="1"/>
       <c r="I65" s="1" t="s">
-        <v>786</v>
+        <v>782</v>
       </c>
       <c r="J65" s="1" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
       <c r="K65" s="1"/>
       <c r="L65" s="1"/>
@@ -12810,7 +12797,7 @@
     </row>
     <row r="66" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B66" s="1" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
       <c r="C66" s="1"/>
       <c r="D66" s="1"/>
@@ -12819,7 +12806,7 @@
       <c r="G66" s="1"/>
       <c r="H66" s="1"/>
       <c r="I66" s="1" t="s">
-        <v>786</v>
+        <v>782</v>
       </c>
       <c r="J66" s="1" t="s">
         <v>608</v>
@@ -13223,7 +13210,7 @@
     </row>
     <row r="83" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B83" s="1" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="C83" s="1"/>
       <c r="D83" s="1"/>
@@ -13239,13 +13226,13 @@
       <c r="N83" s="1"/>
       <c r="O83" s="1"/>
       <c r="P83" s="1" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
     </row>
     <row r="84" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A84" s="9"/>
+      <c r="A84" s="8"/>
       <c r="B84" s="1" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
       <c r="C84" s="1"/>
       <c r="D84" s="1"/>
@@ -13255,12 +13242,12 @@
       <c r="H84" s="1"/>
       <c r="I84" s="1"/>
       <c r="J84" s="1" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
       <c r="K84" s="1"/>
       <c r="L84" s="1"/>
       <c r="M84" s="1" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="N84" s="1" t="s">
         <v>106</v>
@@ -13300,7 +13287,7 @@
         <v>601</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="F86" s="1"/>
       <c r="G86" s="1"/>
@@ -13327,7 +13314,7 @@
         <v>602</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>293</v>
@@ -13410,7 +13397,7 @@
         <v>604</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>52</v>
@@ -13459,7 +13446,7 @@
         <v>605</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>293</v>
@@ -13468,7 +13455,7 @@
         <v>20</v>
       </c>
       <c r="H92" t="s">
-        <v>781</v>
+        <v>777</v>
       </c>
       <c r="I92" s="1"/>
       <c r="J92" s="1"/>
@@ -13513,7 +13500,7 @@
         <v>606</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>293</v>
@@ -13522,7 +13509,7 @@
         <v>20</v>
       </c>
       <c r="H94" t="s">
-        <v>788</v>
+        <v>784</v>
       </c>
       <c r="I94" s="1"/>
       <c r="J94" s="1"/>
@@ -13557,7 +13544,7 @@
       <c r="P95" s="1"/>
     </row>
     <row r="96" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A96" s="9"/>
+      <c r="A96" s="8"/>
       <c r="B96" s="1" t="s">
         <v>607</v>
       </c>
@@ -13577,7 +13564,7 @@
       </c>
       <c r="O96" s="1"/>
       <c r="P96" s="1" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
     </row>
     <row r="97" spans="2:16" x14ac:dyDescent="0.3">
@@ -13619,12 +13606,12 @@
       <c r="N98" s="1"/>
       <c r="O98" s="1"/>
       <c r="P98" s="1" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
     </row>
     <row r="99" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B99" s="1" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
       <c r="C99" s="1"/>
       <c r="D99" s="1"/>
@@ -13633,7 +13620,7 @@
       <c r="G99" s="1"/>
       <c r="H99" s="1"/>
       <c r="I99" s="1" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="J99" s="1" t="s">
         <v>608</v>
@@ -13641,7 +13628,7 @@
       <c r="K99" s="1"/>
       <c r="L99" s="1"/>
       <c r="M99" s="1" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="N99" s="1" t="s">
         <v>106</v>
@@ -13681,7 +13668,7 @@
         <v>609</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>720</v>
+        <v>716</v>
       </c>
       <c r="F101" s="1"/>
       <c r="G101" s="1"/>
@@ -13708,7 +13695,7 @@
         <v>610</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>721</v>
+        <v>717</v>
       </c>
       <c r="F102" s="1"/>
       <c r="G102" s="1"/>
@@ -13735,7 +13722,7 @@
         <v>611</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="F103" s="1"/>
       <c r="G103" s="1"/>
@@ -13762,7 +13749,7 @@
         <v>612</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>723</v>
+        <v>719</v>
       </c>
       <c r="F104" s="1"/>
       <c r="G104" s="1"/>
@@ -13789,7 +13776,7 @@
         <v>613</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="F105" s="1"/>
       <c r="G105" s="1"/>
@@ -13816,7 +13803,7 @@
         <v>385</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="I106" s="1"/>
       <c r="J106" s="1"/>
@@ -13840,7 +13827,7 @@
         <v>615</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>726</v>
+        <v>722</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>293</v>
@@ -13873,7 +13860,7 @@
         <v>616</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
       <c r="F108" s="1"/>
       <c r="G108" s="1"/>
@@ -13900,7 +13887,7 @@
         <v>617</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>727</v>
+        <v>723</v>
       </c>
       <c r="F109" s="1"/>
       <c r="G109" s="1"/>
@@ -13927,7 +13914,7 @@
         <v>618</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>729</v>
+        <v>725</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>52</v>
@@ -13956,7 +13943,7 @@
         <v>621</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="F111" s="1"/>
       <c r="G111" s="1"/>
@@ -13983,7 +13970,7 @@
         <v>622</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="F112" s="1"/>
       <c r="G112" s="1"/>
@@ -13999,7 +13986,7 @@
       <c r="O112" s="1"/>
       <c r="P112" s="1"/>
     </row>
-    <row r="113" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="113" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B113" s="1" t="s">
         <v>10</v>
       </c>
@@ -14010,7 +13997,7 @@
         <v>623</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
       <c r="F113" s="1"/>
       <c r="G113" s="1"/>
@@ -14026,7 +14013,7 @@
       <c r="O113" s="1"/>
       <c r="P113" s="1"/>
     </row>
-    <row r="114" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="114" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B114" s="1" t="s">
         <v>10</v>
       </c>
@@ -14037,7 +14024,7 @@
         <v>624</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="F114" s="1"/>
       <c r="G114" s="1"/>
@@ -14053,7 +14040,7 @@
       <c r="O114" s="1"/>
       <c r="P114" s="1"/>
     </row>
-    <row r="115" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="115" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B115" s="1" t="s">
         <v>10</v>
       </c>
@@ -14064,7 +14051,7 @@
         <v>625</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>734</v>
+        <v>730</v>
       </c>
       <c r="F115" s="1"/>
       <c r="G115" s="1"/>
@@ -14080,7 +14067,7 @@
       <c r="O115" s="1"/>
       <c r="P115" s="1"/>
     </row>
-    <row r="116" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="116" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B116" s="1" t="s">
         <v>10</v>
       </c>
@@ -14091,7 +14078,7 @@
         <v>385</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="F116" s="1"/>
       <c r="G116" s="1"/>
@@ -14106,7 +14093,7 @@
       <c r="O116" s="1"/>
       <c r="P116" s="1"/>
     </row>
-    <row r="117" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="117" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B117" s="1" t="s">
         <v>10</v>
       </c>
@@ -14117,7 +14104,7 @@
         <v>627</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
       <c r="F117" s="1"/>
       <c r="G117" s="1"/>
@@ -14133,7 +14120,7 @@
       <c r="O117" s="1"/>
       <c r="P117" s="1"/>
     </row>
-    <row r="118" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="118" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B118" s="1" t="s">
         <v>10</v>
       </c>
@@ -14144,7 +14131,7 @@
         <v>628</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
       <c r="F118" s="1"/>
       <c r="G118" s="1"/>
@@ -14160,7 +14147,7 @@
       <c r="O118" s="1"/>
       <c r="P118" s="1"/>
     </row>
-    <row r="119" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="119" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B119" s="1" t="s">
         <v>10</v>
       </c>
@@ -14171,7 +14158,7 @@
         <v>629</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>293</v>
@@ -14193,7 +14180,7 @@
       <c r="O119" s="1"/>
       <c r="P119" s="1"/>
     </row>
-    <row r="120" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="120" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B120" s="1" t="s">
         <v>10</v>
       </c>
@@ -14204,7 +14191,7 @@
         <v>631</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="F120" s="1"/>
       <c r="G120" s="1"/>
@@ -14219,7 +14206,7 @@
       <c r="O120" s="1"/>
       <c r="P120" s="1"/>
     </row>
-    <row r="121" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="121" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B121" s="1" t="s">
         <v>10</v>
       </c>
@@ -14230,7 +14217,7 @@
         <v>632</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>740</v>
+        <v>736</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>52</v>
@@ -14248,7 +14235,7 @@
       <c r="O121" s="1"/>
       <c r="P121" s="1"/>
     </row>
-    <row r="122" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="122" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B122" s="1" t="s">
         <v>10</v>
       </c>
@@ -14259,7 +14246,7 @@
         <v>633</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>556</v>
@@ -14268,7 +14255,7 @@
         <v>20</v>
       </c>
       <c r="H122" s="1" t="s">
-        <v>780</v>
+        <v>776</v>
       </c>
       <c r="I122" s="1"/>
       <c r="J122" s="1"/>
@@ -14281,7 +14268,7 @@
       <c r="O122" s="1"/>
       <c r="P122" s="1"/>
     </row>
-    <row r="123" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="123" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B123" s="1" t="s">
         <v>2</v>
       </c>
@@ -14302,7 +14289,7 @@
       <c r="O123" s="1"/>
       <c r="P123" s="1"/>
     </row>
-    <row r="124" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="124" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B124" s="1" t="s">
         <v>59</v>
       </c>
@@ -14316,14 +14303,18 @@
       <c r="J124" s="1"/>
       <c r="K124" s="1"/>
       <c r="L124" s="1"/>
-      <c r="M124" s="1"/>
-      <c r="N124" s="1"/>
+      <c r="M124" s="1" t="s">
+        <v>786</v>
+      </c>
+      <c r="N124" s="1" t="s">
+        <v>787</v>
+      </c>
       <c r="O124" s="1"/>
       <c r="P124" s="1" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="125" spans="1:16" x14ac:dyDescent="0.3">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="125" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B125" s="1" t="s">
         <v>546</v>
       </c>
@@ -14344,7 +14335,7 @@
       <c r="O125" s="1"/>
       <c r="P125" s="1"/>
     </row>
-    <row r="126" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="126" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B126" s="1" t="s">
         <v>10</v>
       </c>
@@ -14355,7 +14346,7 @@
         <v>614</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="F126" s="1"/>
       <c r="G126" s="1"/>
@@ -14370,7 +14361,7 @@
       <c r="O126" s="1"/>
       <c r="P126" s="1"/>
     </row>
-    <row r="127" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="127" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B127" s="1" t="s">
         <v>10</v>
       </c>
@@ -14381,7 +14372,7 @@
         <v>637</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
       <c r="F127" s="1"/>
       <c r="G127" s="1"/>
@@ -14396,8 +14387,7 @@
       <c r="O127" s="1"/>
       <c r="P127" s="1"/>
     </row>
-    <row r="128" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A128" s="8"/>
+    <row r="128" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B128" s="1" t="s">
         <v>607</v>
       </c>
@@ -14406,10 +14396,7 @@
       <c r="E128" s="1"/>
       <c r="F128" s="1"/>
       <c r="G128" s="1"/>
-      <c r="H128" s="1"/>
-      <c r="I128" s="1" t="s">
-        <v>638</v>
-      </c>
+      <c r="I128" s="1"/>
       <c r="J128" s="1"/>
       <c r="K128" s="1"/>
       <c r="L128" s="1"/>
@@ -14418,9 +14405,9 @@
       <c r="O128" s="1"/>
       <c r="P128" s="1"/>
     </row>
-    <row r="129" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="129" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B129" s="1" t="s">
-        <v>546</v>
+        <v>2</v>
       </c>
       <c r="C129" s="1"/>
       <c r="D129" s="1"/>
@@ -14429,7 +14416,7 @@
       <c r="G129" s="1"/>
       <c r="H129" s="1"/>
       <c r="I129" s="1" t="s">
-        <v>544</v>
+        <v>599</v>
       </c>
       <c r="J129" s="1"/>
       <c r="K129" s="1"/>
@@ -14439,18 +14426,18 @@
       <c r="O129" s="1"/>
       <c r="P129" s="1"/>
     </row>
-    <row r="130" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A130" s="8"/>
+    <row r="130" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B130" s="1" t="s">
-        <v>639</v>
+        <v>546</v>
       </c>
       <c r="C130" s="1"/>
       <c r="D130" s="1"/>
       <c r="E130" s="1"/>
       <c r="F130" s="1"/>
       <c r="G130" s="1"/>
+      <c r="H130" s="1"/>
       <c r="I130" s="1" t="s">
-        <v>640</v>
+        <v>544</v>
       </c>
       <c r="J130" s="1"/>
       <c r="K130" s="1"/>
@@ -14460,7 +14447,7 @@
       <c r="O130" s="1"/>
       <c r="P130" s="1"/>
     </row>
-    <row r="131" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="131" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B131" s="1" t="s">
         <v>10</v>
       </c>
@@ -14471,7 +14458,7 @@
         <v>634</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>744</v>
+        <v>740</v>
       </c>
       <c r="F131" s="1"/>
       <c r="G131" s="1"/>
@@ -14487,7 +14474,7 @@
       <c r="O131" s="1"/>
       <c r="P131" s="1"/>
     </row>
-    <row r="132" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="132" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B132" s="1" t="s">
         <v>10</v>
       </c>
@@ -14498,7 +14485,7 @@
         <v>635</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>745</v>
+        <v>741</v>
       </c>
       <c r="F132" s="1"/>
       <c r="G132" s="1"/>
@@ -14514,7 +14501,7 @@
       <c r="O132" s="1"/>
       <c r="P132" s="1"/>
     </row>
-    <row r="133" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="133" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B133" s="1" t="s">
         <v>10</v>
       </c>
@@ -14525,7 +14512,7 @@
         <v>636</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>746</v>
+        <v>742</v>
       </c>
       <c r="F133" s="1"/>
       <c r="G133" s="1"/>
@@ -14541,7 +14528,7 @@
       <c r="O133" s="1"/>
       <c r="P133" s="1"/>
     </row>
-    <row r="134" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="134" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B134" s="1" t="s">
         <v>10</v>
       </c>
@@ -14549,10 +14536,10 @@
         <v>16</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>641</v>
+        <v>785</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>747</v>
+        <v>743</v>
       </c>
       <c r="F134" s="1"/>
       <c r="G134" s="1"/>
@@ -14567,7 +14554,7 @@
       <c r="O134" s="1"/>
       <c r="P134" s="1"/>
     </row>
-    <row r="135" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="135" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B135" s="1" t="s">
         <v>546</v>
       </c>
@@ -14586,7 +14573,7 @@
       <c r="O135" s="1"/>
       <c r="P135" s="1"/>
     </row>
-    <row r="136" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="136" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B136" s="1" t="s">
         <v>2</v>
       </c>
@@ -14609,7 +14596,7 @@
       </c>
       <c r="P136" s="1"/>
     </row>
-    <row r="137" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="137" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B137" s="1" t="s">
         <v>59</v>
       </c>
@@ -14630,9 +14617,9 @@
         <v>545</v>
       </c>
     </row>
-    <row r="138" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="138" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B138" s="1" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
       <c r="C138" s="1"/>
       <c r="D138" s="1"/>
@@ -14642,12 +14629,12 @@
       <c r="H138" s="1"/>
       <c r="I138" s="1"/>
       <c r="J138" s="1" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
       <c r="K138" s="1"/>
       <c r="L138" s="1"/>
       <c r="M138" s="1" t="s">
-        <v>787</v>
+        <v>783</v>
       </c>
       <c r="N138" s="1" t="s">
         <v>106</v>
@@ -14655,7 +14642,7 @@
       <c r="O138" s="1"/>
       <c r="P138" s="1"/>
     </row>
-    <row r="139" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="139" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B139" s="1" t="s">
         <v>546</v>
       </c>
@@ -14676,18 +14663,18 @@
       <c r="O139" s="1"/>
       <c r="P139" s="1"/>
     </row>
-    <row r="140" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="140" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B140" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>556</v>
@@ -14696,7 +14683,7 @@
         <v>12</v>
       </c>
       <c r="H140" s="1" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="I140" s="1"/>
       <c r="J140" s="1"/>
@@ -14709,7 +14696,7 @@
       <c r="O140" s="1"/>
       <c r="P140" s="1"/>
     </row>
-    <row r="141" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="141" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B141" s="1" t="s">
         <v>10</v>
       </c>
@@ -14717,10 +14704,10 @@
         <v>24</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>749</v>
+        <v>745</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>557</v>
@@ -14729,7 +14716,7 @@
         <v>20</v>
       </c>
       <c r="H141" s="1" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="I141" s="1"/>
       <c r="J141" s="1"/>
@@ -14742,7 +14729,7 @@
       <c r="O141" s="1"/>
       <c r="P141" s="1"/>
     </row>
-    <row r="142" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="142" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B142" s="1" t="s">
         <v>10</v>
       </c>
@@ -14750,10 +14737,10 @@
         <v>16</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>750</v>
+        <v>746</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>293</v>
@@ -14762,7 +14749,7 @@
         <v>5</v>
       </c>
       <c r="H142" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="I142" s="1"/>
       <c r="J142" s="1"/>
@@ -14775,7 +14762,7 @@
       <c r="O142" s="1"/>
       <c r="P142" s="1"/>
     </row>
-    <row r="143" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="143" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B143" s="1" t="s">
         <v>10</v>
       </c>
@@ -14783,10 +14770,10 @@
         <v>24</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>751</v>
+        <v>747</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>557</v>
@@ -14808,7 +14795,7 @@
       <c r="O143" s="1"/>
       <c r="P143" s="1"/>
     </row>
-    <row r="144" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="144" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B144" s="1" t="s">
         <v>10</v>
       </c>
@@ -14816,10 +14803,10 @@
         <v>24</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="F144" s="1"/>
       <c r="G144" s="1"/>
@@ -14843,10 +14830,10 @@
         <v>16</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>293</v>
@@ -14855,7 +14842,7 @@
         <v>5</v>
       </c>
       <c r="H145" t="s">
-        <v>781</v>
+        <v>777</v>
       </c>
       <c r="I145" s="1"/>
       <c r="J145" s="1"/>
@@ -14876,10 +14863,10 @@
         <v>16</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>293</v>
@@ -14888,7 +14875,7 @@
         <v>5</v>
       </c>
       <c r="H146" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="I146" s="1"/>
       <c r="J146" s="1"/>
@@ -14909,10 +14896,10 @@
         <v>91</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="F147" s="1"/>
       <c r="G147" s="1"/>
@@ -14936,10 +14923,10 @@
         <v>9</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>756</v>
+        <v>752</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>556</v>
@@ -14969,10 +14956,10 @@
         <v>9</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>757</v>
+        <v>753</v>
       </c>
       <c r="F149" s="1"/>
       <c r="G149" s="1"/>
@@ -14996,10 +14983,10 @@
         <v>16</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>758</v>
+        <v>754</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>293</v>
@@ -15008,7 +14995,7 @@
         <v>5</v>
       </c>
       <c r="H150" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="I150" s="1"/>
       <c r="J150" s="1"/>
@@ -15029,10 +15016,10 @@
         <v>9</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>759</v>
+        <v>755</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>556</v>
@@ -15062,10 +15049,10 @@
         <v>9</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>760</v>
+        <v>756</v>
       </c>
       <c r="F152" s="1"/>
       <c r="G152" s="1"/>
@@ -15089,10 +15076,10 @@
         <v>9</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>761</v>
+        <v>757</v>
       </c>
       <c r="F153" s="1"/>
       <c r="G153" s="1"/>
@@ -15116,10 +15103,10 @@
         <v>91</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>52</v>
@@ -15145,10 +15132,10 @@
         <v>16</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>293</v>
@@ -15178,10 +15165,10 @@
         <v>91</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>764</v>
+        <v>760</v>
       </c>
       <c r="F156" s="1"/>
       <c r="G156" s="1"/>
@@ -15205,10 +15192,10 @@
         <v>16</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>765</v>
+        <v>761</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>293</v>
@@ -15217,7 +15204,7 @@
         <v>20</v>
       </c>
       <c r="H157" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="I157" s="1"/>
       <c r="J157" s="1"/>
@@ -15238,10 +15225,10 @@
         <v>91</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
       <c r="F158" s="1"/>
       <c r="G158" s="1"/>
@@ -15349,10 +15336,10 @@
         <v>24</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="F163" s="1" t="s">
         <v>557</v>
@@ -15361,7 +15348,7 @@
         <v>12</v>
       </c>
       <c r="H163" s="1" t="s">
-        <v>782</v>
+        <v>778</v>
       </c>
       <c r="I163" s="1"/>
       <c r="J163" s="1"/>
@@ -15382,10 +15369,10 @@
         <v>9</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>556</v>
@@ -15394,7 +15381,7 @@
         <v>5</v>
       </c>
       <c r="H164" s="1" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="I164" s="1"/>
       <c r="J164" s="1"/>

--- a/resource/Script/script_InertiaLucis.xlsx
+++ b/resource/Script/script_InertiaLucis.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\usosctheater\resource\Script\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{639301A1-142E-49DD-8F6B-B1F741365F9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1918D9DD-DB79-44E5-BD28-C9ED589D90BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="3" xr2:uid="{12160F34-6A21-4287-85A5-86880D8D3A1A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{12160F34-6A21-4287-85A5-86880D8D3A1A}"/>
   </bookViews>
   <sheets>
     <sheet name="Scene1" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2795" uniqueCount="889">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2796" uniqueCount="890">
   <si>
     <t>se_trans_out|se_trans_in</t>
   </si>
@@ -3044,6 +3044,10 @@
   </si>
   <si>
     <t>anger3 face_serious lip_smile</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>0</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -17026,7 +17030,7 @@
       <c r="J37" s="1"/>
       <c r="K37" s="1"/>
       <c r="L37" s="1" t="s">
-        <v>52</v>
+        <v>889</v>
       </c>
       <c r="M37" s="1"/>
       <c r="N37" s="1"/>
@@ -17852,7 +17856,7 @@
       <c r="J71" s="1"/>
       <c r="K71" s="1"/>
       <c r="L71" s="1" t="s">
-        <v>52</v>
+        <v>889</v>
       </c>
       <c r="M71" s="1"/>
       <c r="N71" s="1"/>
@@ -18816,6 +18820,9 @@
       </c>
       <c r="G110" s="1" t="s">
         <v>20</v>
+      </c>
+      <c r="H110" t="s">
+        <v>771</v>
       </c>
       <c r="I110" s="1"/>
       <c r="J110" s="1"/>
